--- a/reports/screener_2026-08-04.xlsx
+++ b/reports/screener_2026-08-04.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>13.80000019073486</v>
+        <v>13.77000045776367</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -644,13 +644,13 @@
         <v>14.5</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.827584891483705</v>
+        <v>-5.034479601629849</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8067631497914509</v>
+        <v>0.8632232831013459</v>
       </c>
       <c r="Z2" t="n">
-        <v>-31.78361767760132</v>
+        <v>-31.93191283888014</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>sem sinal (-4.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>18.70000076293945</v>
+        <v>18.71999931335449</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         <v>18.40999984741211</v>
       </c>
       <c r="X3" t="n">
-        <v>1.575235838842826</v>
+        <v>1.683864576381078</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7490385359935988</v>
+        <v>0.7603597066369503</v>
       </c>
       <c r="Z3" t="n">
-        <v>-18.9723148118655</v>
+        <v>-18.88566047062824</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
@@ -847,7 +847,7 @@
         <v>-15.54216785793608</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.902194329293153</v>
+        <v>0.9314921168579823</v>
       </c>
       <c r="Z4" t="n">
         <v>-59.66775351546308</v>
@@ -932,7 +932,7 @@
         <v>0.34</v>
       </c>
       <c r="T5" t="n">
-        <v>34.41999816894531</v>
+        <v>34.38999938964844</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -941,20 +941,20 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>31.48999977111816</v>
       </c>
       <c r="X5" t="n">
-        <v>9.304536103917238</v>
+        <v>9.209271640548188</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.349293683544027</v>
+        <v>2.29029317618129</v>
       </c>
       <c r="Z5" t="n">
-        <v>-15.82294281555076</v>
+        <v>-15.8963074028451</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>-7.794509454510957</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4099551578881351</v>
+        <v>0.4147431669964095</v>
       </c>
       <c r="Z6" t="n">
         <v>-45.15279189419018</v>
@@ -1134,7 +1134,7 @@
         <v>0.24</v>
       </c>
       <c r="T7" t="n">
-        <v>4.809999942779541</v>
+        <v>4.829999923706055</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
@@ -1143,16 +1143,16 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.0569391092512</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.882286448554999</v>
+        <v>3.887910250049635</v>
       </c>
       <c r="Z7" t="n">
-        <v>-39.50409920702425</v>
+        <v>-39.25255723688181</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>10.27000045776367</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
@@ -1244,13 +1244,13 @@
         <v>10.89000034332275</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.693295372017482</v>
+        <v>-5.785124835438637</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3991824608350278</v>
+        <v>0.4149256395485635</v>
       </c>
       <c r="Z8" t="n">
-        <v>-27.88223540198856</v>
+        <v>-27.95245878273644</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>sem sinal (-5.7% do topo; Em Alta)</t>
+          <t>sem sinal (-5.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>14.15999984741211</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1340,13 +1340,13 @@
         <v>14.47000026702881</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.142366371084758</v>
+        <v>-2.211476451922989</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.472838898531202</v>
+        <v>1.476407452409882</v>
       </c>
       <c r="Z9" t="n">
-        <v>-23.9689549748106</v>
+        <v>-24.02265044518985</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>16.13999938964844</v>
+        <v>16.1299991607666</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.02497416098241</v>
+        <v>-14.42971440667444</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6285486923606332</v>
+        <v>0.6542277135423189</v>
       </c>
       <c r="Z10" t="n">
-        <v>-53.85128519147116</v>
+        <v>-53.87987860709323</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>sem sinal (-16.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>-5.641026236680191</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5431217900149019</v>
+        <v>0.546716943327443</v>
       </c>
       <c r="Z11" t="n">
         <v>-25.98880057902984</v>
@@ -1624,7 +1624,7 @@
         <v>0.27</v>
       </c>
       <c r="T12" t="n">
-        <v>31.59000015258789</v>
+        <v>31.77000045776367</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
@@ -1636,13 +1636,13 @@
         <v>33.59000015258789</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.95415299468498</v>
+        <v>-5.418278316631686</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6391760782987143</v>
+        <v>0.6644429962957882</v>
       </c>
       <c r="Z12" t="n">
-        <v>-23.03719460312219</v>
+        <v>-22.59865935805391</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>sem sinal (-6.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -1724,25 +1724,25 @@
         <v>0.77</v>
       </c>
       <c r="T13" t="n">
-        <v>10.98999977111816</v>
+        <v>11</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>11.33961009979248</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.083089503057201</v>
+        <v>-2.994901031021302</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.3659423336614514</v>
+        <v>0.3902845169637474</v>
       </c>
       <c r="Z13" t="n">
-        <v>-22.35245300984857</v>
+        <v>-22.28179313121694</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.07692160973182</v>
+        <v>-11.23330245815745</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4984746988709627</v>
+        <v>0.4986285084487594</v>
       </c>
       <c r="Z14" t="n">
         <v>-31.89242973610049</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>sem sinal (-13.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-11.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
-        <v>8.229999542236328</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
@@ -1928,13 +1928,13 @@
         <v>8.520000457763672</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.403766431292699</v>
+        <v>-3.638502382170861</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9633078619644886</v>
+        <v>0.9655940223092898</v>
       </c>
       <c r="Z15" t="n">
-        <v>-17.80318060245866</v>
+        <v>-18.00292491802473</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Lateral)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>42.56999969482422</v>
+        <v>42.65999984741211</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
@@ -2023,16 +2023,16 @@
         </is>
       </c>
       <c r="W16" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.114981534826853</v>
+        <v>-1.750341671079958</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6141399829152128</v>
+        <v>0.6393345129941977</v>
       </c>
       <c r="Z16" t="n">
-        <v>-13.40156180119051</v>
+        <v>-13.21847811061877</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>21.51000022888184</v>
+        <v>21.53000068664551</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>22.95999908447266</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.315326277915323</v>
+        <v>-6.228216266760334</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3057034044167466</v>
+        <v>0.313305375907764</v>
       </c>
       <c r="Z17" t="n">
-        <v>-40.27513055823297</v>
+        <v>-40.21959709863278</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>sem sinal (-6.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>0.4</v>
       </c>
       <c r="T18" t="n">
-        <v>13.85999965667725</v>
+        <v>13.82999992370605</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
@@ -2224,13 +2224,13 @@
         <v>14.28999996185303</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.009099414441296</v>
+        <v>-3.219034565254986</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3510442272256908</v>
+        <v>0.3608440285448147</v>
       </c>
       <c r="Z18" t="n">
-        <v>-19.98332848962821</v>
+        <v>-20.1565232109858</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>0.25</v>
       </c>
       <c r="T19" t="n">
-        <v>11.69999980926514</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
@@ -2324,13 +2324,13 @@
         <v>12.98999977111816</v>
       </c>
       <c r="X19" t="n">
-        <v>-9.930715816648439</v>
+        <v>-9.776747701821053</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4377777871753775</v>
+        <v>0.4503882234795601</v>
       </c>
       <c r="Z19" t="n">
-        <v>-32.20486497008408</v>
+        <v>-32.0889731959941</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>sem sinal (-9.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-9.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
-        <v>9.760000228881836</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -2422,13 +2422,13 @@
         <v>10.47999954223633</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.870222755762178</v>
+        <v>-7.061066826728657</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.7733800208474594</v>
+        <v>0.8317791503799855</v>
       </c>
       <c r="Z20" t="n">
-        <v>-45.99996903973109</v>
+        <v>-46.11062737099443</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>sem sinal (-6.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>14.88000011444092</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2526,13 +2526,13 @@
         <v>14.38436412811279</v>
       </c>
       <c r="X21" t="n">
-        <v>3.445657951326853</v>
+        <v>3.515179473396013</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.6894183542789591</v>
+        <v>0.7022694166953245</v>
       </c>
       <c r="Z21" t="n">
-        <v>-4.975091345719996</v>
+        <v>-4.911229058844335</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>48.02999877929688</v>
+        <v>48.15999984741211</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="W22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3757740721689</v>
+        <v>-1.794455651889282</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.464355180240822</v>
+        <v>1.495614491879106</v>
       </c>
       <c r="Z22" t="n">
-        <v>-12.05357833906487</v>
+        <v>-11.81553692654328</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.4% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         <v>-23.23232493513931</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.4498483221531314</v>
+        <v>0.5510624531771436</v>
       </c>
       <c r="Z23" t="n">
         <v>-28.95697958964646</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="n">
-        <v>22.67000007629395</v>
+        <v>22.65999984741211</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
@@ -2822,13 +2822,13 @@
         <v>23.52000045776367</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.613947129789075</v>
+        <v>-3.65646510890133</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.4703925278737459</v>
+        <v>0.4639123450760227</v>
       </c>
       <c r="Z24" t="n">
-        <v>-36.83740695398845</v>
+        <v>-36.86526934415628</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>6.190000057220459</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2924,13 +2924,13 @@
         <v>6.099999904632568</v>
       </c>
       <c r="X25" t="n">
-        <v>1.475412360573003</v>
+        <v>1.311474179619254</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.8643793255779708</v>
+        <v>0.9244067233135493</v>
       </c>
       <c r="Z25" t="n">
-        <v>-30.44943457826056</v>
+        <v>-30.56179670534441</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="W26" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.039510814348012</v>
+        <v>-2.595420936543091</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6421717495758301</v>
+        <v>0.6487002486233108</v>
       </c>
       <c r="Z26" t="n">
         <v>-39.23809414818174</v>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
         <v>0.19</v>
       </c>
       <c r="T27" t="n">
-        <v>32.40999984741211</v>
+        <v>32.45999908447266</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3126,13 +3126,13 @@
         <v>32.34000015258789</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2164492717809052</v>
+        <v>0.3710542093957381</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.4046669620440112</v>
+        <v>0.4145512524650695</v>
       </c>
       <c r="Z27" t="n">
-        <v>-10.4943367388541</v>
+        <v>-10.35625543997335</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -3214,7 +3214,7 @@
         <v>0.16</v>
       </c>
       <c r="T28" t="n">
-        <v>17.67000007629395</v>
+        <v>17.64999961853027</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
@@ -3226,13 +3226,13 @@
         <v>18.00869941711426</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.88075403434429</v>
+        <v>-1.991814013193538</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.3322370035835256</v>
+        <v>0.332478831663171</v>
       </c>
       <c r="Z28" t="n">
-        <v>-39.00144315229424</v>
+        <v>-39.07049082284214</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
         <v>0.14</v>
       </c>
       <c r="T30" t="n">
-        <v>29.18000030517578</v>
+        <v>29.20000076293945</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3398,13 +3398,13 @@
         <v>28.93000030517578</v>
       </c>
       <c r="X30" t="n">
-        <v>0.8641548474345173</v>
+        <v>0.9332888175440646</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.8795242178721391</v>
+        <v>0.7461038850131747</v>
       </c>
       <c r="Z30" t="n">
-        <v>-19.96506739747932</v>
+        <v>-19.9102101228942</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
@@ -3486,7 +3486,7 @@
         <v>0.05</v>
       </c>
       <c r="T31" t="n">
-        <v>31.67000007629395</v>
+        <v>31.88999938964844</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -3498,13 +3498,13 @@
         <v>34.59999847412109</v>
       </c>
       <c r="X31" t="n">
-        <v>-8.468203835380594</v>
+        <v>-7.832367641575444</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4101142392811051</v>
+        <v>0.4668809400071821</v>
       </c>
       <c r="Z31" t="n">
-        <v>-16.52609060982171</v>
+        <v>-15.94622945716574</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>sem sinal (-8.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3586,9 +3586,13 @@
         <v>0.82</v>
       </c>
       <c r="T32" t="n">
-        <v>13.88000011444092</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>13.89000034332275</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
           <t>Em Alta</t>
@@ -3598,26 +3602,26 @@
         <v>13.93000030517578</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.3589389062417014</v>
+        <v>-0.2871497557553226</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.4648921766669861</v>
+        <v>0.4777709256040814</v>
       </c>
       <c r="Z32" t="n">
-        <v>-7.775919251367869</v>
+        <v>-7.709473868925565</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
       <c r="AB32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>sem sinal (-0.4% do topo; Em Alta)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3690,7 @@
         <v>0.09</v>
       </c>
       <c r="T33" t="n">
-        <v>12.34000015258789</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -3702,13 +3706,13 @@
         <v>12.21000003814697</v>
       </c>
       <c r="X33" t="n">
-        <v>1.064701998646744</v>
+        <v>1.146603954835057</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4801167098318198</v>
+        <v>0.4891199691892933</v>
       </c>
       <c r="Z33" t="n">
-        <v>-12.66808172226156</v>
+        <v>-12.59730869465475</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -3790,7 +3794,7 @@
         <v>0.01</v>
       </c>
       <c r="T34" t="n">
-        <v>3.509999990463257</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3802,13 +3806,13 @@
         <v>3.630000114440918</v>
       </c>
       <c r="X34" t="n">
-        <v>-3.305788435109824</v>
+        <v>-3.030306612851064</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.970570319291225</v>
+        <v>1.94398223412281</v>
       </c>
       <c r="Z34" t="n">
-        <v>-53.93700730737312</v>
+        <v>-53.80577383475578</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
@@ -3821,7 +3825,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>sem sinal (-3.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3863,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3884,9 +3888,13 @@
         <v>0.41</v>
       </c>
       <c r="T35" t="n">
-        <v>15.76000022888184</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
+        <v>15.73999977111816</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Em Alta</t>
@@ -3896,26 +3904,26 @@
         <v>16</v>
       </c>
       <c r="X35" t="n">
-        <v>-1.499998569488525</v>
+        <v>-1.625001430511475</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5015008615098066</v>
+        <v>0.5031908497405458</v>
       </c>
       <c r="Z35" t="n">
-        <v>-21.32127795576485</v>
+        <v>-21.42112633357526</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
       </c>
       <c r="AB35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>sem sinal (-1.5% do topo; Em Alta)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3961,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3978,42 +3986,38 @@
         <v>0.26</v>
       </c>
       <c r="T36" t="n">
-        <v>54.56000137329102</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+        <v>54.58000183105469</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>55.45000076293945</v>
       </c>
       <c r="X36" t="n">
-        <v>-1.6050484714209</v>
+        <v>-1.568979116166647</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.6671301151158817</v>
+        <v>0.6935723995080588</v>
       </c>
       <c r="Z36" t="n">
-        <v>-1.782174396699265</v>
+        <v>-1.746169971787725</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
       </c>
       <c r="AB36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-1.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4078,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="n">
-        <v>16.05999946594238</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
@@ -4086,13 +4090,13 @@
         <v>16.50238800048828</v>
       </c>
       <c r="X37" t="n">
-        <v>-2.680754655222073</v>
+        <v>-2.741353332707663</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4219459257233043</v>
+        <v>0.3780987335746765</v>
       </c>
       <c r="Z37" t="n">
-        <v>-11.70417295525581</v>
+        <v>-11.75916249766079</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
@@ -4172,7 +4176,7 @@
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="n">
-        <v>5.739999771118164</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
@@ -4184,13 +4188,13 @@
         <v>5.980000019073486</v>
       </c>
       <c r="X38" t="n">
-        <v>-4.013382060030612</v>
+        <v>-4.180601993354738</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3171561702603102</v>
+        <v>0.3413517682079079</v>
       </c>
       <c r="Z38" t="n">
-        <v>-9.930614717402875</v>
+        <v>-10.08752613823156</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -4203,7 +4207,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>sem sinal (-4.0% do topo; Em Alta)</t>
+          <t>sem sinal (-4.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4276,7 @@
         <v>0.17</v>
       </c>
       <c r="T39" t="n">
-        <v>28.96999931335449</v>
+        <v>28.98999977111816</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
@@ -4281,16 +4285,16 @@
         </is>
       </c>
       <c r="W39" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="X39" t="n">
-        <v>-2.62185104754793</v>
+        <v>-2.521856105487796</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.4675328592650685</v>
+        <v>0.4585670544652213</v>
       </c>
       <c r="Z39" t="n">
-        <v>-17.88122217201873</v>
+        <v>-17.82452858601662</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
@@ -4303,7 +4307,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>sem sinal (-2.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4347,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -4370,42 +4374,38 @@
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
-        <v>3.990000009536743</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+        <v>3.980000019073486</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Lateral</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2512560405862674</v>
+        <v>-1.240699457364081</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3249604087435989</v>
+        <v>0.3397859788070529</v>
       </c>
       <c r="Z40" t="n">
-        <v>-47.39487826523337</v>
+        <v>-47.52672054954634</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
       </c>
       <c r="AB40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-1.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
         <v>0.1</v>
       </c>
       <c r="T41" t="n">
-        <v>25.89999961853027</v>
+        <v>25.94000053405762</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
@@ -4486,13 +4486,13 @@
         <v>26.54999923706055</v>
       </c>
       <c r="X41" t="n">
-        <v>-2.448209556341352</v>
+        <v>-2.297546969988029</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.3078920261327238</v>
+        <v>0.3204600291852687</v>
       </c>
       <c r="Z41" t="n">
-        <v>-9.756101289115104</v>
+        <v>-9.616725280529771</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>sem sinal (-2.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -4579,17 +4579,17 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.136750177362035</v>
+        <v>-1.716736616428904</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.7308910824142447</v>
+        <v>0.7492472057827413</v>
       </c>
       <c r="Z42" t="n">
         <v>-51.55226338988712</v>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>sem sinal (-2.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
         <v>0.09</v>
       </c>
       <c r="T43" t="n">
-        <v>25.53000068664551</v>
+        <v>25.52000045776367</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
@@ -4686,13 +4686,13 @@
         <v>26.54129028320312</v>
       </c>
       <c r="X43" t="n">
-        <v>-3.810250314761898</v>
+        <v>-3.847928320522476</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.4266377347335869</v>
+        <v>0.4382982088489977</v>
       </c>
       <c r="Z43" t="n">
-        <v>-16.09314234825725</v>
+        <v>-16.1260090838117</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
-        <v>39.91999816894531</v>
+        <v>39.88000106811523</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
@@ -4784,13 +4784,13 @@
         <v>41.59000015258789</v>
       </c>
       <c r="X44" t="n">
-        <v>-4.015393069284867</v>
+        <v>-4.111563063714618</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.3393867390812401</v>
+        <v>0.3472681647085662</v>
       </c>
       <c r="Z44" t="n">
-        <v>-10.32490672535449</v>
+        <v>-10.41475501974751</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>sem sinal (-4.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
         <v>-0.3695146656611636</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.2763423225712353</v>
+        <v>0.276996554383814</v>
       </c>
       <c r="Z45" t="n">
         <v>-19.52861762955214</v>
@@ -4985,7 +4985,7 @@
         <v>0.2490637839864807</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.5599891789530637</v>
+        <v>0.5773657686803957</v>
       </c>
       <c r="Z46" t="n">
         <v>-11.63035442969306</v>
@@ -5083,7 +5083,7 @@
         <v>2.592590074316825</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.9947347017401169</v>
+        <v>1.050219188724266</v>
       </c>
       <c r="Z47" t="n">
         <v>-4.846668292073931</v>
@@ -5160,7 +5160,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>18.36000061035156</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -5172,13 +5172,13 @@
         <v>18.95059394836426</v>
       </c>
       <c r="X48" t="n">
-        <v>-3.116489855789839</v>
+        <v>-3.169259858192319</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.6479071115808102</v>
+        <v>0.6530980276971341</v>
       </c>
       <c r="Z48" t="n">
-        <v>-13.54917614654679</v>
+        <v>-13.59627956295444</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Em Alta)</t>
+          <t>sem sinal (-3.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
         <v>0.98</v>
       </c>
       <c r="T49" t="n">
-        <v>41.86000061035156</v>
+        <v>41.83000183105469</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -5270,13 +5270,13 @@
         <v>42.58000183105469</v>
       </c>
       <c r="X49" t="n">
-        <v>-1.690937505263346</v>
+        <v>-1.761390248351291</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.057706325626756</v>
+        <v>1.062189422680989</v>
       </c>
       <c r="Z49" t="n">
-        <v>-2.287580622655827</v>
+        <v>-2.357605784163819</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
-        <v>11.25</v>
+        <v>11.22999954223633</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -5365,16 +5365,16 @@
         </is>
       </c>
       <c r="W50" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="X50" t="n">
-        <v>-0.2659550858277293</v>
+        <v>-0.9700230059208503</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.4067004617248168</v>
+        <v>0.453655816120157</v>
       </c>
       <c r="Z50" t="n">
-        <v>-15.63968699969552</v>
+        <v>-15.78966432210376</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>sem sinal (-0.3% do topo; Em Alta)</t>
+          <t>sem sinal (-1.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="W51" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="X51" t="n">
-        <v>-15.08858334804334</v>
+        <v>-13.77171901443089</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.7733825992368389</v>
+        <v>0.7852289995706897</v>
       </c>
       <c r="Z51" t="n">
         <v>-35.0381176456114</v>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>sem sinal (-15.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5554,25 +5554,25 @@
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
-        <v>42.7400016784668</v>
+        <v>42.59999847412109</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="X52" t="n">
-        <v>-0.8352594162397753</v>
+        <v>-1.66205269107873</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.2830500133925513</v>
+        <v>0.2961385606308177</v>
       </c>
       <c r="Z52" t="n">
-        <v>-28.34142326319988</v>
+        <v>-28.57615489558209</v>
       </c>
       <c r="AA52" t="b">
         <v>1</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-1.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
         <v>0.51</v>
       </c>
       <c r="T53" t="n">
-        <v>46.47999954223633</v>
+        <v>46.47000122070312</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -5670,13 +5670,13 @@
         <v>47.20000076293945</v>
       </c>
       <c r="X53" t="n">
-        <v>-1.525426290392051</v>
+        <v>-1.54660917465389</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.294721036412365</v>
+        <v>0.3054422974649885</v>
       </c>
       <c r="Z53" t="n">
-        <v>-12.28837738045169</v>
+        <v>-12.30724504425947</v>
       </c>
       <c r="AA53" t="b">
         <v>1</v>
@@ -5758,7 +5758,7 @@
         <v>0.62</v>
       </c>
       <c r="T54" t="n">
-        <v>15.86999988555908</v>
+        <v>15.85999965667725</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
@@ -5770,13 +5770,13 @@
         <v>16.1299991607666</v>
       </c>
       <c r="X54" t="n">
-        <v>-1.611898876225126</v>
+        <v>-1.673896578656264</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.4992510251209511</v>
+        <v>0.5026875344367467</v>
       </c>
       <c r="Z54" t="n">
-        <v>-6.606872970890388</v>
+        <v>-6.665723169568172</v>
       </c>
       <c r="AA54" t="b">
         <v>1</v>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>sem sinal (-1.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
-        <v>34.38999938964844</v>
+        <v>34.41999816894531</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
@@ -5868,13 +5868,13 @@
         <v>36.04999923706055</v>
       </c>
       <c r="X55" t="n">
-        <v>-4.604715346860743</v>
+        <v>-4.521500978118032</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.029722809751753</v>
+        <v>1.042350809061489</v>
       </c>
       <c r="Z55" t="n">
-        <v>-23.4961679399445</v>
+        <v>-23.42943279559827</v>
       </c>
       <c r="AA55" t="b">
         <v>1</v>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>sem sinal (-4.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
-        <v>32.54000091552734</v>
+        <v>32.52999877929688</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
@@ -5966,13 +5966,13 @@
         <v>34.11000061035156</v>
       </c>
       <c r="X56" t="n">
-        <v>-4.602754813049637</v>
+        <v>-4.632077991154282</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.3208393753274065</v>
+        <v>0.3407202430182495</v>
       </c>
       <c r="Z56" t="n">
-        <v>-11.74458379734276</v>
+        <v>-11.77171172208459</v>
       </c>
       <c r="AA56" t="b">
         <v>1</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="n">
-        <v>35.7599983215332</v>
+        <v>35.72000122070312</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
@@ -6064,13 +6064,13 @@
         <v>37.43000030517578</v>
       </c>
       <c r="X57" t="n">
-        <v>-4.461667031863881</v>
+        <v>-4.568525435561376</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.5349471935445591</v>
+        <v>0.5729195927514248</v>
       </c>
       <c r="Z57" t="n">
-        <v>-26.6009905058514</v>
+        <v>-26.683086359357</v>
       </c>
       <c r="AA57" t="b">
         <v>1</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>sem sinal (-4.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
         <v>-22.99651127977449</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.4618399328149727</v>
+        <v>0.4625716770496124</v>
       </c>
       <c r="Z59" t="n">
         <v>-58.21108758197513</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="n">
-        <v>8.359999656677246</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
@@ -6336,13 +6336,13 @@
         <v>8.420000076293945</v>
       </c>
       <c r="X60" t="n">
-        <v>-0.7125940507486161</v>
+        <v>-0.4750589250663406</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.9821578388053023</v>
+        <v>0.9844379148982479</v>
       </c>
       <c r="Z60" t="n">
-        <v>-14.203450461814</v>
+        <v>-13.99819085227123</v>
       </c>
       <c r="AA60" t="b">
         <v>1</v>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>sem sinal (-0.7% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="n">
-        <v>3.640000104904175</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
@@ -6434,13 +6434,13 @@
         <v>3.720000028610229</v>
       </c>
       <c r="X61" t="n">
-        <v>-2.150535566956491</v>
+        <v>-1.881718621086936</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.2595261902486549</v>
+        <v>0.2638674047482383</v>
       </c>
       <c r="Z61" t="n">
-        <v>-50.23798493811276</v>
+        <v>-50.10127623984077</v>
       </c>
       <c r="AA61" t="b">
         <v>1</v>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Lateral)</t>
+          <t>sem sinal (-1.9% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
-        <v>49.0099983215332</v>
+        <v>49.02999877929688</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -6536,13 +6536,13 @@
         <v>48.20000076293945</v>
       </c>
       <c r="X62" t="n">
-        <v>1.680492833553138</v>
+        <v>1.721987558547089</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.4230048894247058</v>
+        <v>0.4259377639779914</v>
       </c>
       <c r="Z62" t="n">
-        <v>-9.717892472299406</v>
+        <v>-9.681042824481189</v>
       </c>
       <c r="AA62" t="b">
         <v>1</v>
@@ -6717,7 +6717,7 @@
         <v>1.042271571538156</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.9979251937593372</v>
+        <v>1.027214157115012</v>
       </c>
       <c r="Z64" t="n">
         <v>-3.591158037740838</v>
@@ -6796,7 +6796,7 @@
         <v>0.9</v>
       </c>
       <c r="T65" t="n">
-        <v>42.81000137329102</v>
+        <v>42.83000183105469</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
@@ -6805,16 +6805,16 @@
         </is>
       </c>
       <c r="W65" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="X65" t="n">
-        <v>-1.879440006302158</v>
+        <v>-1.791971043940976</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.5533997670312797</v>
+        <v>0.5795485283308205</v>
       </c>
       <c r="Z65" t="n">
-        <v>-12.12993808415603</v>
+        <v>-12.05160580638767</v>
       </c>
       <c r="AA65" t="b">
         <v>1</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Lateral)</t>
+          <t>sem sinal (-1.8% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
         <v>0.47</v>
       </c>
       <c r="T66" t="n">
-        <v>9.579999923706055</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
@@ -6908,13 +6908,13 @@
         <v>10.30000019073486</v>
       </c>
       <c r="X66" t="n">
-        <v>-6.990293725202735</v>
+        <v>-7.087383324199359</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.2999282217792989</v>
+        <v>0.3136289472081446</v>
       </c>
       <c r="Z66" t="n">
-        <v>-37.32231289272016</v>
+        <v>-37.38773995136825</v>
       </c>
       <c r="AA66" t="b">
         <v>1</v>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>sem sinal (-7.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -6994,42 +6994,38 @@
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="n">
-        <v>76.33000183105469</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+        <v>76.26000213623047</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>76.08999633789062</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="X67" t="n">
-        <v>0.3154231892695591</v>
+        <v>-0.02621479206399435</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.7869302695467675</v>
+        <v>0.7916633959946799</v>
       </c>
       <c r="Z67" t="n">
-        <v>-16.68849646055893</v>
+        <v>-16.76489865737816</v>
       </c>
       <c r="AA67" t="b">
         <v>1</v>
       </c>
       <c r="AB67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7094,7 @@
         <v>-0.03</v>
       </c>
       <c r="T68" t="n">
-        <v>7.53000020980835</v>
+        <v>7.510000228881836</v>
       </c>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
@@ -7110,13 +7106,13 @@
         <v>8.689999580383301</v>
       </c>
       <c r="X68" t="n">
-        <v>-13.34867004129113</v>
+        <v>-13.57881943015488</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.634616499534768</v>
+        <v>0.6498876194712899</v>
       </c>
       <c r="Z68" t="n">
-        <v>-38.17733972790999</v>
+        <v>-38.3415431796785</v>
       </c>
       <c r="AA68" t="b">
         <v>1</v>
@@ -7129,7 +7125,7 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>sem sinal (-13.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7358,7 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>13.80000019073486</v>
+        <v>13.77000045776367</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -7374,13 +7370,13 @@
         <v>14.5</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.827584891483705</v>
+        <v>-5.034479601629849</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8067631497914509</v>
+        <v>0.8632232831013459</v>
       </c>
       <c r="Z2" t="n">
-        <v>-31.78361767760132</v>
+        <v>-31.93191283888014</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
@@ -7393,7 +7389,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>sem sinal (-4.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7456,7 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>18.70000076293945</v>
+        <v>18.71999931335449</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -7476,13 +7472,13 @@
         <v>18.40999984741211</v>
       </c>
       <c r="X3" t="n">
-        <v>1.575235838842826</v>
+        <v>1.683864576381078</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7490385359935988</v>
+        <v>0.7603597066369503</v>
       </c>
       <c r="Z3" t="n">
-        <v>-18.9723148118655</v>
+        <v>-18.88566047062824</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
@@ -7577,7 +7573,7 @@
         <v>-15.54216785793608</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.902194329293153</v>
+        <v>0.9314921168579823</v>
       </c>
       <c r="Z4" t="n">
         <v>-59.66775351546308</v>
@@ -7662,7 +7658,7 @@
         <v>0.34</v>
       </c>
       <c r="T5" t="n">
-        <v>34.41999816894531</v>
+        <v>34.38999938964844</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -7671,20 +7667,20 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>31.48999977111816</v>
       </c>
       <c r="X5" t="n">
-        <v>9.304536103917238</v>
+        <v>9.209271640548188</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.349293683544027</v>
+        <v>2.29029317618129</v>
       </c>
       <c r="Z5" t="n">
-        <v>-15.82294281555076</v>
+        <v>-15.8963074028451</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -7779,7 +7775,7 @@
         <v>-7.794509454510957</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4099551578881351</v>
+        <v>0.4147431669964095</v>
       </c>
       <c r="Z6" t="n">
         <v>-45.15279189419018</v>
@@ -7864,7 +7860,7 @@
         <v>0.24</v>
       </c>
       <c r="T7" t="n">
-        <v>4.809999942779541</v>
+        <v>4.829999923706055</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
@@ -7873,16 +7869,16 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.0569391092512</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.882286448554999</v>
+        <v>3.887910250049635</v>
       </c>
       <c r="Z7" t="n">
-        <v>-39.50409920702425</v>
+        <v>-39.25255723688181</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
@@ -7895,7 +7891,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7958,7 @@
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>10.27000045776367</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
@@ -7974,13 +7970,13 @@
         <v>10.89000034332275</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.693295372017482</v>
+        <v>-5.785124835438637</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3991824608350278</v>
+        <v>0.4149256395485635</v>
       </c>
       <c r="Z8" t="n">
-        <v>-27.88223540198856</v>
+        <v>-27.95245878273644</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -7993,7 +7989,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>sem sinal (-5.7% do topo; Em Alta)</t>
+          <t>sem sinal (-5.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8050,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>14.15999984741211</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -8070,13 +8066,13 @@
         <v>14.47000026702881</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.142366371084758</v>
+        <v>-2.211476451922989</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.472838898531202</v>
+        <v>1.476407452409882</v>
       </c>
       <c r="Z9" t="n">
-        <v>-23.9689549748106</v>
+        <v>-24.02265044518985</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -8156,7 +8152,7 @@
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>16.13999938964844</v>
+        <v>16.1299991607666</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
@@ -8165,16 +8161,16 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.02497416098241</v>
+        <v>-14.42971440667444</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6285486923606332</v>
+        <v>0.6542277135423189</v>
       </c>
       <c r="Z10" t="n">
-        <v>-53.85128519147116</v>
+        <v>-53.87987860709323</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -8187,7 +8183,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>sem sinal (-16.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8265,7 @@
         <v>-5.641026236680191</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5431217900149019</v>
+        <v>0.546716943327443</v>
       </c>
       <c r="Z11" t="n">
         <v>-25.98880057902984</v>
@@ -8354,7 +8350,7 @@
         <v>0.27</v>
       </c>
       <c r="T12" t="n">
-        <v>31.59000015258789</v>
+        <v>31.77000045776367</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
@@ -8366,13 +8362,13 @@
         <v>33.59000015258789</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.95415299468498</v>
+        <v>-5.418278316631686</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6391760782987143</v>
+        <v>0.6644429962957882</v>
       </c>
       <c r="Z12" t="n">
-        <v>-23.03719460312219</v>
+        <v>-22.59865935805391</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -8385,7 +8381,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>sem sinal (-6.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -8454,25 +8450,25 @@
         <v>0.77</v>
       </c>
       <c r="T13" t="n">
-        <v>10.98999977111816</v>
+        <v>11</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>11.33961009979248</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.083089503057201</v>
+        <v>-2.994901031021302</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.3659423336614514</v>
+        <v>0.3902845169637474</v>
       </c>
       <c r="Z13" t="n">
-        <v>-22.35245300984857</v>
+        <v>-22.28179313121694</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
@@ -8485,7 +8481,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -8563,13 +8559,13 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.07692160973182</v>
+        <v>-11.23330245815745</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4984746988709627</v>
+        <v>0.4986285084487594</v>
       </c>
       <c r="Z14" t="n">
         <v>-31.89242973610049</v>
@@ -8585,7 +8581,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>sem sinal (-13.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-11.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8642,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
-        <v>8.229999542236328</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
@@ -8658,13 +8654,13 @@
         <v>8.520000457763672</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.403766431292699</v>
+        <v>-3.638502382170861</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9633078619644886</v>
+        <v>0.9655940223092898</v>
       </c>
       <c r="Z15" t="n">
-        <v>-17.80318060245866</v>
+        <v>-18.00292491802473</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -8677,7 +8673,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Lateral)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8740,7 @@
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>42.56999969482422</v>
+        <v>42.65999984741211</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
@@ -8753,16 +8749,16 @@
         </is>
       </c>
       <c r="W16" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.114981534826853</v>
+        <v>-1.750341671079958</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6141399829152128</v>
+        <v>0.6393345129941977</v>
       </c>
       <c r="Z16" t="n">
-        <v>-13.40156180119051</v>
+        <v>-13.21847811061877</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -8775,7 +8771,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8838,7 @@
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>21.51000022888184</v>
+        <v>21.53000068664551</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
@@ -8854,13 +8850,13 @@
         <v>22.95999908447266</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.315326277915323</v>
+        <v>-6.228216266760334</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3057034044167466</v>
+        <v>0.313305375907764</v>
       </c>
       <c r="Z17" t="n">
-        <v>-40.27513055823297</v>
+        <v>-40.21959709863278</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -8873,7 +8869,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>sem sinal (-6.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8938,7 @@
         <v>0.4</v>
       </c>
       <c r="T18" t="n">
-        <v>13.85999965667725</v>
+        <v>13.82999992370605</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
@@ -8954,13 +8950,13 @@
         <v>14.28999996185303</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.009099414441296</v>
+        <v>-3.219034565254986</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3510442272256908</v>
+        <v>0.3608440285448147</v>
       </c>
       <c r="Z18" t="n">
-        <v>-19.98332848962821</v>
+        <v>-20.1565232109858</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -8973,7 +8969,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9038,7 @@
         <v>0.25</v>
       </c>
       <c r="T19" t="n">
-        <v>11.69999980926514</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
@@ -9054,13 +9050,13 @@
         <v>12.98999977111816</v>
       </c>
       <c r="X19" t="n">
-        <v>-9.930715816648439</v>
+        <v>-9.776747701821053</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4377777871753775</v>
+        <v>0.4503882234795601</v>
       </c>
       <c r="Z19" t="n">
-        <v>-32.20486497008408</v>
+        <v>-32.0889731959941</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -9073,7 +9069,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>sem sinal (-9.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-9.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9136,7 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
-        <v>9.760000228881836</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -9152,13 +9148,13 @@
         <v>10.47999954223633</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.870222755762178</v>
+        <v>-7.061066826728657</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.7733800208474594</v>
+        <v>0.8317791503799855</v>
       </c>
       <c r="Z20" t="n">
-        <v>-45.99996903973109</v>
+        <v>-46.11062737099443</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -9171,7 +9167,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>sem sinal (-6.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9236,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>14.88000011444092</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -9256,13 +9252,13 @@
         <v>14.38436412811279</v>
       </c>
       <c r="X21" t="n">
-        <v>3.445657951326853</v>
+        <v>3.515179473396013</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.6894183542789591</v>
+        <v>0.7022694166953245</v>
       </c>
       <c r="Z21" t="n">
-        <v>-4.975091345719996</v>
+        <v>-4.911229058844335</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
@@ -9342,7 +9338,7 @@
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>48.02999877929688</v>
+        <v>48.15999984741211</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -9351,16 +9347,16 @@
         </is>
       </c>
       <c r="W22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3757740721689</v>
+        <v>-1.794455651889282</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.464355180240822</v>
+        <v>1.495614491879106</v>
       </c>
       <c r="Z22" t="n">
-        <v>-12.05357833906487</v>
+        <v>-11.81553692654328</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -9373,7 +9369,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.4% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9453,7 @@
         <v>-23.23232493513931</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.4498483221531314</v>
+        <v>0.5510624531771436</v>
       </c>
       <c r="Z23" t="n">
         <v>-28.95697958964646</v>
@@ -9540,7 +9536,7 @@
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="n">
-        <v>22.67000007629395</v>
+        <v>22.65999984741211</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
@@ -9552,13 +9548,13 @@
         <v>23.52000045776367</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.613947129789075</v>
+        <v>-3.65646510890133</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.4703925278737459</v>
+        <v>0.4639123450760227</v>
       </c>
       <c r="Z24" t="n">
-        <v>-36.83740695398845</v>
+        <v>-36.86526934415628</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -9571,7 +9567,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9634,7 @@
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>6.190000057220459</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -9654,13 +9650,13 @@
         <v>6.099999904632568</v>
       </c>
       <c r="X25" t="n">
-        <v>1.475412360573003</v>
+        <v>1.311474179619254</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.8643793255779708</v>
+        <v>0.9244067233135493</v>
       </c>
       <c r="Z25" t="n">
-        <v>-30.44943457826056</v>
+        <v>-30.56179670534441</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
@@ -9749,13 +9745,13 @@
         </is>
       </c>
       <c r="W26" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.039510814348012</v>
+        <v>-2.595420936543091</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6421717495758301</v>
+        <v>0.6487002486233108</v>
       </c>
       <c r="Z26" t="n">
         <v>-39.23809414818174</v>
@@ -9771,7 +9767,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9836,7 @@
         <v>0.19</v>
       </c>
       <c r="T27" t="n">
-        <v>32.40999984741211</v>
+        <v>32.45999908447266</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -9856,13 +9852,13 @@
         <v>32.34000015258789</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2164492717809052</v>
+        <v>0.3710542093957381</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.4046669620440112</v>
+        <v>0.4145512524650695</v>
       </c>
       <c r="Z27" t="n">
-        <v>-10.4943367388541</v>
+        <v>-10.35625543997335</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -9944,7 +9940,7 @@
         <v>0.16</v>
       </c>
       <c r="T28" t="n">
-        <v>17.67000007629395</v>
+        <v>17.64999961853027</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
@@ -9956,13 +9952,13 @@
         <v>18.00869941711426</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.88075403434429</v>
+        <v>-1.991814013193538</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.3322370035835256</v>
+        <v>0.332478831663171</v>
       </c>
       <c r="Z28" t="n">
-        <v>-39.00144315229424</v>
+        <v>-39.07049082284214</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
@@ -9975,7 +9971,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10108,7 @@
         <v>0.14</v>
       </c>
       <c r="T30" t="n">
-        <v>29.18000030517578</v>
+        <v>29.20000076293945</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -10128,13 +10124,13 @@
         <v>28.93000030517578</v>
       </c>
       <c r="X30" t="n">
-        <v>0.8641548474345173</v>
+        <v>0.9332888175440646</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.8795242178721391</v>
+        <v>0.7461038850131747</v>
       </c>
       <c r="Z30" t="n">
-        <v>-19.96506739747932</v>
+        <v>-19.9102101228942</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
@@ -10216,7 +10212,7 @@
         <v>0.05</v>
       </c>
       <c r="T31" t="n">
-        <v>31.67000007629395</v>
+        <v>31.88999938964844</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -10228,13 +10224,13 @@
         <v>34.59999847412109</v>
       </c>
       <c r="X31" t="n">
-        <v>-8.468203835380594</v>
+        <v>-7.832367641575444</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4101142392811051</v>
+        <v>0.4668809400071821</v>
       </c>
       <c r="Z31" t="n">
-        <v>-16.52609060982171</v>
+        <v>-15.94622945716574</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -10247,7 +10243,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>sem sinal (-8.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -10287,7 +10283,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -10316,9 +10312,13 @@
         <v>0.82</v>
       </c>
       <c r="T32" t="n">
-        <v>13.88000011444092</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>13.89000034332275</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
           <t>Em Alta</t>
@@ -10328,26 +10328,26 @@
         <v>13.93000030517578</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.3589389062417014</v>
+        <v>-0.2871497557553226</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.4648921766669861</v>
+        <v>0.4777709256040814</v>
       </c>
       <c r="Z32" t="n">
-        <v>-7.775919251367869</v>
+        <v>-7.709473868925565</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
       <c r="AB32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>sem sinal (-0.4% do topo; Em Alta)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10416,7 @@
         <v>0.09</v>
       </c>
       <c r="T33" t="n">
-        <v>12.34000015258789</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -10432,13 +10432,13 @@
         <v>12.21000003814697</v>
       </c>
       <c r="X33" t="n">
-        <v>1.064701998646744</v>
+        <v>1.146603954835057</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4801167098318198</v>
+        <v>0.4891199691892933</v>
       </c>
       <c r="Z33" t="n">
-        <v>-12.66808172226156</v>
+        <v>-12.59730869465475</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -10520,7 +10520,7 @@
         <v>0.01</v>
       </c>
       <c r="T34" t="n">
-        <v>3.509999990463257</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -10532,13 +10532,13 @@
         <v>3.630000114440918</v>
       </c>
       <c r="X34" t="n">
-        <v>-3.305788435109824</v>
+        <v>-3.030306612851064</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.970570319291225</v>
+        <v>1.94398223412281</v>
       </c>
       <c r="Z34" t="n">
-        <v>-53.93700730737312</v>
+        <v>-53.80577383475578</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>sem sinal (-3.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -10614,9 +10614,13 @@
         <v>0.41</v>
       </c>
       <c r="T35" t="n">
-        <v>15.76000022888184</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
+        <v>15.73999977111816</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Em Alta</t>
@@ -10626,26 +10630,26 @@
         <v>16</v>
       </c>
       <c r="X35" t="n">
-        <v>-1.499998569488525</v>
+        <v>-1.625001430511475</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5015008615098066</v>
+        <v>0.5031908497405458</v>
       </c>
       <c r="Z35" t="n">
-        <v>-21.32127795576485</v>
+        <v>-21.42112633357526</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
       </c>
       <c r="AB35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>sem sinal (-1.5% do topo; Em Alta)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10687,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -10708,42 +10712,38 @@
         <v>0.26</v>
       </c>
       <c r="T36" t="n">
-        <v>54.56000137329102</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+        <v>54.58000183105469</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>55.45000076293945</v>
       </c>
       <c r="X36" t="n">
-        <v>-1.6050484714209</v>
+        <v>-1.568979116166647</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.6671301151158817</v>
+        <v>0.6935723995080588</v>
       </c>
       <c r="Z36" t="n">
-        <v>-1.782174396699265</v>
+        <v>-1.746169971787725</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
       </c>
       <c r="AB36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-1.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="n">
-        <v>16.05999946594238</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
@@ -10816,13 +10816,13 @@
         <v>16.50238800048828</v>
       </c>
       <c r="X37" t="n">
-        <v>-2.680754655222073</v>
+        <v>-2.741353332707663</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4219459257233043</v>
+        <v>0.3780987335746765</v>
       </c>
       <c r="Z37" t="n">
-        <v>-11.70417295525581</v>
+        <v>-11.75916249766079</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="n">
-        <v>5.739999771118164</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
@@ -10914,13 +10914,13 @@
         <v>5.980000019073486</v>
       </c>
       <c r="X38" t="n">
-        <v>-4.013382060030612</v>
+        <v>-4.180601993354738</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3171561702603102</v>
+        <v>0.3413517682079079</v>
       </c>
       <c r="Z38" t="n">
-        <v>-9.930614717402875</v>
+        <v>-10.08752613823156</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>sem sinal (-4.0% do topo; Em Alta)</t>
+          <t>sem sinal (-4.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
         <v>0.17</v>
       </c>
       <c r="T39" t="n">
-        <v>28.96999931335449</v>
+        <v>28.98999977111816</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
@@ -11011,16 +11011,16 @@
         </is>
       </c>
       <c r="W39" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="X39" t="n">
-        <v>-2.62185104754793</v>
+        <v>-2.521856105487796</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.4675328592650685</v>
+        <v>0.4585670544652213</v>
       </c>
       <c r="Z39" t="n">
-        <v>-17.88122217201873</v>
+        <v>-17.82452858601662</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>sem sinal (-2.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -11100,42 +11100,38 @@
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
-        <v>3.990000009536743</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+        <v>3.980000019073486</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Lateral</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2512560405862674</v>
+        <v>-1.240699457364081</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3249604087435989</v>
+        <v>0.3397859788070529</v>
       </c>
       <c r="Z40" t="n">
-        <v>-47.39487826523337</v>
+        <v>-47.52672054954634</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
       </c>
       <c r="AB40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-1.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11200,7 @@
         <v>0.1</v>
       </c>
       <c r="T41" t="n">
-        <v>25.89999961853027</v>
+        <v>25.94000053405762</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
@@ -11216,13 +11212,13 @@
         <v>26.54999923706055</v>
       </c>
       <c r="X41" t="n">
-        <v>-2.448209556341352</v>
+        <v>-2.297546969988029</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.3078920261327238</v>
+        <v>0.3204600291852687</v>
       </c>
       <c r="Z41" t="n">
-        <v>-9.756101289115104</v>
+        <v>-9.616725280529771</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
@@ -11235,7 +11231,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>sem sinal (-2.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -11309,17 +11305,17 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.136750177362035</v>
+        <v>-1.716736616428904</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.7308910824142447</v>
+        <v>0.7492472057827413</v>
       </c>
       <c r="Z42" t="n">
         <v>-51.55226338988712</v>
@@ -11335,7 +11331,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>sem sinal (-2.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11400,7 @@
         <v>0.09</v>
       </c>
       <c r="T43" t="n">
-        <v>25.53000068664551</v>
+        <v>25.52000045776367</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
@@ -11416,13 +11412,13 @@
         <v>26.54129028320312</v>
       </c>
       <c r="X43" t="n">
-        <v>-3.810250314761898</v>
+        <v>-3.847928320522476</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.4266377347335869</v>
+        <v>0.4382982088489977</v>
       </c>
       <c r="Z43" t="n">
-        <v>-16.09314234825725</v>
+        <v>-16.1260090838117</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
@@ -11502,7 +11498,7 @@
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
-        <v>39.91999816894531</v>
+        <v>39.88000106811523</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
@@ -11514,13 +11510,13 @@
         <v>41.59000015258789</v>
       </c>
       <c r="X44" t="n">
-        <v>-4.015393069284867</v>
+        <v>-4.111563063714618</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.3393867390812401</v>
+        <v>0.3472681647085662</v>
       </c>
       <c r="Z44" t="n">
-        <v>-10.32490672535449</v>
+        <v>-10.41475501974751</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
@@ -11533,7 +11529,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>sem sinal (-4.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -11617,7 +11613,7 @@
         <v>-0.3695146656611636</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.2763423225712353</v>
+        <v>0.276996554383814</v>
       </c>
       <c r="Z45" t="n">
         <v>-19.52861762955214</v>
@@ -11715,7 +11711,7 @@
         <v>0.2490637839864807</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.5599891789530637</v>
+        <v>0.5773657686803957</v>
       </c>
       <c r="Z46" t="n">
         <v>-11.63035442969306</v>
@@ -11813,7 +11809,7 @@
         <v>2.592590074316825</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.9947347017401169</v>
+        <v>1.050219188724266</v>
       </c>
       <c r="Z47" t="n">
         <v>-4.846668292073931</v>
@@ -11890,7 +11886,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>18.36000061035156</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -11902,13 +11898,13 @@
         <v>18.95059394836426</v>
       </c>
       <c r="X48" t="n">
-        <v>-3.116489855789839</v>
+        <v>-3.169259858192319</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.6479071115808102</v>
+        <v>0.6530980276971341</v>
       </c>
       <c r="Z48" t="n">
-        <v>-13.54917614654679</v>
+        <v>-13.59627956295444</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
@@ -11921,7 +11917,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Em Alta)</t>
+          <t>sem sinal (-3.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11980,7 @@
         <v>0.98</v>
       </c>
       <c r="T49" t="n">
-        <v>41.86000061035156</v>
+        <v>41.83000183105469</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -12000,13 +11996,13 @@
         <v>42.58000183105469</v>
       </c>
       <c r="X49" t="n">
-        <v>-1.690937505263346</v>
+        <v>-1.761390248351291</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.057706325626756</v>
+        <v>1.062189422680989</v>
       </c>
       <c r="Z49" t="n">
-        <v>-2.287580622655827</v>
+        <v>-2.357605784163819</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
@@ -12086,7 +12082,7 @@
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
-        <v>11.25</v>
+        <v>11.22999954223633</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -12095,16 +12091,16 @@
         </is>
       </c>
       <c r="W50" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="X50" t="n">
-        <v>-0.2659550858277293</v>
+        <v>-0.9700230059208503</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.4067004617248168</v>
+        <v>0.453655816120157</v>
       </c>
       <c r="Z50" t="n">
-        <v>-15.63968699969552</v>
+        <v>-15.78966432210376</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
@@ -12117,7 +12113,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>sem sinal (-0.3% do topo; Em Alta)</t>
+          <t>sem sinal (-1.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -12195,13 +12191,13 @@
         </is>
       </c>
       <c r="W51" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="X51" t="n">
-        <v>-15.08858334804334</v>
+        <v>-13.77171901443089</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.7733825992368389</v>
+        <v>0.7852289995706897</v>
       </c>
       <c r="Z51" t="n">
         <v>-35.0381176456114</v>
@@ -12217,7 +12213,7 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>sem sinal (-15.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -12284,25 +12280,25 @@
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
-        <v>42.7400016784668</v>
+        <v>42.59999847412109</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="X52" t="n">
-        <v>-0.8352594162397753</v>
+        <v>-1.66205269107873</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.2830500133925513</v>
+        <v>0.2961385606308177</v>
       </c>
       <c r="Z52" t="n">
-        <v>-28.34142326319988</v>
+        <v>-28.57615489558209</v>
       </c>
       <c r="AA52" t="b">
         <v>1</v>
@@ -12315,7 +12311,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-1.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12380,7 @@
         <v>0.51</v>
       </c>
       <c r="T53" t="n">
-        <v>46.47999954223633</v>
+        <v>46.47000122070312</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -12400,13 +12396,13 @@
         <v>47.20000076293945</v>
       </c>
       <c r="X53" t="n">
-        <v>-1.525426290392051</v>
+        <v>-1.54660917465389</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.294721036412365</v>
+        <v>0.3054422974649885</v>
       </c>
       <c r="Z53" t="n">
-        <v>-12.28837738045169</v>
+        <v>-12.30724504425947</v>
       </c>
       <c r="AA53" t="b">
         <v>1</v>
@@ -12488,7 +12484,7 @@
         <v>0.62</v>
       </c>
       <c r="T54" t="n">
-        <v>15.86999988555908</v>
+        <v>15.85999965667725</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
@@ -12500,13 +12496,13 @@
         <v>16.1299991607666</v>
       </c>
       <c r="X54" t="n">
-        <v>-1.611898876225126</v>
+        <v>-1.673896578656264</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.4992510251209511</v>
+        <v>0.5026875344367467</v>
       </c>
       <c r="Z54" t="n">
-        <v>-6.606872970890388</v>
+        <v>-6.665723169568172</v>
       </c>
       <c r="AA54" t="b">
         <v>1</v>
@@ -12519,7 +12515,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>sem sinal (-1.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12582,7 @@
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
-        <v>34.38999938964844</v>
+        <v>34.41999816894531</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
@@ -12598,13 +12594,13 @@
         <v>36.04999923706055</v>
       </c>
       <c r="X55" t="n">
-        <v>-4.604715346860743</v>
+        <v>-4.521500978118032</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.029722809751753</v>
+        <v>1.042350809061489</v>
       </c>
       <c r="Z55" t="n">
-        <v>-23.4961679399445</v>
+        <v>-23.42943279559827</v>
       </c>
       <c r="AA55" t="b">
         <v>1</v>
@@ -12617,7 +12613,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>sem sinal (-4.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12680,7 @@
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
-        <v>32.54000091552734</v>
+        <v>32.52999877929688</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
@@ -12696,13 +12692,13 @@
         <v>34.11000061035156</v>
       </c>
       <c r="X56" t="n">
-        <v>-4.602754813049637</v>
+        <v>-4.632077991154282</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.3208393753274065</v>
+        <v>0.3407202430182495</v>
       </c>
       <c r="Z56" t="n">
-        <v>-11.74458379734276</v>
+        <v>-11.77171172208459</v>
       </c>
       <c r="AA56" t="b">
         <v>1</v>
@@ -12782,7 +12778,7 @@
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="n">
-        <v>35.7599983215332</v>
+        <v>35.72000122070312</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
@@ -12794,13 +12790,13 @@
         <v>37.43000030517578</v>
       </c>
       <c r="X57" t="n">
-        <v>-4.461667031863881</v>
+        <v>-4.568525435561376</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.5349471935445591</v>
+        <v>0.5729195927514248</v>
       </c>
       <c r="Z57" t="n">
-        <v>-26.6009905058514</v>
+        <v>-26.683086359357</v>
       </c>
       <c r="AA57" t="b">
         <v>1</v>
@@ -12813,7 +12809,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>sem sinal (-4.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12967,7 @@
         <v>-22.99651127977449</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.4618399328149727</v>
+        <v>0.4625716770496124</v>
       </c>
       <c r="Z59" t="n">
         <v>-58.21108758197513</v>
@@ -13054,7 +13050,7 @@
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="n">
-        <v>8.359999656677246</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
@@ -13066,13 +13062,13 @@
         <v>8.420000076293945</v>
       </c>
       <c r="X60" t="n">
-        <v>-0.7125940507486161</v>
+        <v>-0.4750589250663406</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.9821578388053023</v>
+        <v>0.9844379148982479</v>
       </c>
       <c r="Z60" t="n">
-        <v>-14.203450461814</v>
+        <v>-13.99819085227123</v>
       </c>
       <c r="AA60" t="b">
         <v>1</v>
@@ -13085,7 +13081,7 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>sem sinal (-0.7% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13148,7 @@
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="n">
-        <v>3.640000104904175</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
@@ -13164,13 +13160,13 @@
         <v>3.720000028610229</v>
       </c>
       <c r="X61" t="n">
-        <v>-2.150535566956491</v>
+        <v>-1.881718621086936</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.2595261902486549</v>
+        <v>0.2638674047482383</v>
       </c>
       <c r="Z61" t="n">
-        <v>-50.23798493811276</v>
+        <v>-50.10127623984077</v>
       </c>
       <c r="AA61" t="b">
         <v>1</v>
@@ -13183,7 +13179,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Lateral)</t>
+          <t>sem sinal (-1.9% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13246,7 @@
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
-        <v>49.0099983215332</v>
+        <v>49.02999877929688</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -13266,13 +13262,13 @@
         <v>48.20000076293945</v>
       </c>
       <c r="X62" t="n">
-        <v>1.680492833553138</v>
+        <v>1.721987558547089</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.4230048894247058</v>
+        <v>0.4259377639779914</v>
       </c>
       <c r="Z62" t="n">
-        <v>-9.717892472299406</v>
+        <v>-9.681042824481189</v>
       </c>
       <c r="AA62" t="b">
         <v>1</v>
@@ -13447,7 +13443,7 @@
         <v>1.042271571538156</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.9979251937593372</v>
+        <v>1.027214157115012</v>
       </c>
       <c r="Z64" t="n">
         <v>-3.591158037740838</v>
@@ -13526,7 +13522,7 @@
         <v>0.9</v>
       </c>
       <c r="T65" t="n">
-        <v>42.81000137329102</v>
+        <v>42.83000183105469</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
@@ -13535,16 +13531,16 @@
         </is>
       </c>
       <c r="W65" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="X65" t="n">
-        <v>-1.879440006302158</v>
+        <v>-1.791971043940976</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.5533997670312797</v>
+        <v>0.5795485283308205</v>
       </c>
       <c r="Z65" t="n">
-        <v>-12.12993808415603</v>
+        <v>-12.05160580638767</v>
       </c>
       <c r="AA65" t="b">
         <v>1</v>
@@ -13557,7 +13553,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Lateral)</t>
+          <t>sem sinal (-1.8% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13622,7 @@
         <v>0.47</v>
       </c>
       <c r="T66" t="n">
-        <v>9.579999923706055</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
@@ -13638,13 +13634,13 @@
         <v>10.30000019073486</v>
       </c>
       <c r="X66" t="n">
-        <v>-6.990293725202735</v>
+        <v>-7.087383324199359</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.2999282217792989</v>
+        <v>0.3136289472081446</v>
       </c>
       <c r="Z66" t="n">
-        <v>-37.32231289272016</v>
+        <v>-37.38773995136825</v>
       </c>
       <c r="AA66" t="b">
         <v>1</v>
@@ -13657,7 +13653,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>sem sinal (-7.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13697,7 +13693,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -13724,42 +13720,38 @@
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="n">
-        <v>76.33000183105469</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+        <v>76.26000213623047</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>76.08999633789062</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="X67" t="n">
-        <v>0.3154231892695591</v>
+        <v>-0.02621479206399435</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.7869302695467675</v>
+        <v>0.7916633959946799</v>
       </c>
       <c r="Z67" t="n">
-        <v>-16.68849646055893</v>
+        <v>-16.76489865737816</v>
       </c>
       <c r="AA67" t="b">
         <v>1</v>
       </c>
       <c r="AB67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13828,7 +13820,7 @@
         <v>-0.03</v>
       </c>
       <c r="T68" t="n">
-        <v>7.53000020980835</v>
+        <v>7.510000228881836</v>
       </c>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
@@ -13840,13 +13832,13 @@
         <v>8.689999580383301</v>
       </c>
       <c r="X68" t="n">
-        <v>-13.34867004129113</v>
+        <v>-13.57881943015488</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.634616499534768</v>
+        <v>0.6498876194712899</v>
       </c>
       <c r="Z68" t="n">
-        <v>-38.17733972790999</v>
+        <v>-38.3415431796785</v>
       </c>
       <c r="AA68" t="b">
         <v>1</v>
@@ -13859,7 +13851,7 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>sem sinal (-13.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13920,7 @@
         <v>0.85</v>
       </c>
       <c r="T69" t="n">
-        <v>31.84000015258789</v>
+        <v>31.81999969482422</v>
       </c>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
@@ -13940,13 +13932,13 @@
         <v>35.95353698730469</v>
       </c>
       <c r="X69" t="n">
-        <v>-11.44125774376329</v>
+        <v>-11.49688636736919</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.046542924309523</v>
+        <v>1.073302525685695</v>
       </c>
       <c r="Z69" t="n">
-        <v>-22.76889806613722</v>
+        <v>-22.81741836457223</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -13959,7 +13951,7 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>sem sinal (-11.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-11.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14020,7 @@
         <v>7.25</v>
       </c>
       <c r="T70" t="n">
-        <v>27.53000068664551</v>
+        <v>27.5</v>
       </c>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
@@ -14040,13 +14032,13 @@
         <v>27.93385887145996</v>
       </c>
       <c r="X70" t="n">
-        <v>-1.445765823736855</v>
+        <v>-1.553164829307685</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.4037789986269111</v>
+        <v>0.4304806765088075</v>
       </c>
       <c r="Z70" t="n">
-        <v>-16.05179202484853</v>
+        <v>-16.14327418318847</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -14059,7 +14051,7 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>sem sinal (-1.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14120,7 @@
         <v>0.72</v>
       </c>
       <c r="T71" t="n">
-        <v>27.73999977111816</v>
+        <v>27.70999908447266</v>
       </c>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
@@ -14137,16 +14129,16 @@
         </is>
       </c>
       <c r="W71" t="n">
-        <v>30.3700008392334</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="X71" t="n">
-        <v>-8.659864983334719</v>
+        <v>-8.668427998972517</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.598836482049957</v>
+        <v>0.6003815277069408</v>
       </c>
       <c r="Z71" t="n">
-        <v>-21.45648352707087</v>
+        <v>-21.54142799156917</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -14237,13 +14229,13 @@
         </is>
       </c>
       <c r="W72" t="n">
-        <v>4.070000171661377</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="X72" t="n">
-        <v>-4.422605876297203</v>
+        <v>-2.506263268008835</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.3779810008446386</v>
+        <v>0.389739217060219</v>
       </c>
       <c r="Z72" t="n">
         <v>-19.0219927402037</v>
@@ -14259,7 +14251,7 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>sem sinal (-4.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14312,7 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="n">
-        <v>21.25</v>
+        <v>21.20999908447266</v>
       </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
@@ -14329,16 +14321,16 @@
         </is>
       </c>
       <c r="W73" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.09403129916892849</v>
+        <v>-0.6557437681293021</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.3159367208904453</v>
+        <v>0.3075530531786483</v>
       </c>
       <c r="Z73" t="n">
-        <v>-22.84646610948897</v>
+        <v>-22.99169961498498</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -14351,7 +14343,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>sem sinal (-0.1% do topo; Em Alta)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14412,7 @@
         <v>1.63</v>
       </c>
       <c r="T74" t="n">
-        <v>7.150000095367432</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
@@ -14432,13 +14424,13 @@
         <v>7.820000171661377</v>
       </c>
       <c r="X74" t="n">
-        <v>-8.567775723611037</v>
+        <v>-8.695655885533228</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.3579549891814168</v>
+        <v>0.3560923649018772</v>
       </c>
       <c r="Z74" t="n">
-        <v>-40.08037594874582</v>
+        <v>-40.16418153574355</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -14451,7 +14443,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>sem sinal (-8.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-8.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14527,7 @@
         <v>-1.737041110989757</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.3839141157961991</v>
+        <v>0.3886358037628182</v>
       </c>
       <c r="Z75" t="n">
         <v>-1.737041110989757</v>
@@ -14612,25 +14604,25 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="n">
-        <v>54.84999847412109</v>
+        <v>54.7599983215332</v>
       </c>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W76" t="n">
         <v>57.45000076293945</v>
       </c>
       <c r="X76" t="n">
-        <v>-4.525678423481594</v>
+        <v>-4.682336650448837</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.5755738197855067</v>
+        <v>0.5234597985131034</v>
       </c>
       <c r="Z76" t="n">
-        <v>-15.25549905021393</v>
+        <v>-15.39455134244078</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -14643,7 +14635,7 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>sem sinal (-4.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14723,7 @@
         <v>1.785712613134938</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.164759636037021</v>
+        <v>1.147665515198136</v>
       </c>
       <c r="Z77" t="n">
         <v>-1.0416739102864</v>
@@ -14814,7 +14806,7 @@
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="n">
-        <v>3.279999971389771</v>
+        <v>3.269999980926514</v>
       </c>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
@@ -14826,13 +14818,13 @@
         <v>3.420000076293945</v>
       </c>
       <c r="X78" t="n">
-        <v>-4.093570227515453</v>
+        <v>-4.385967602959184</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.3924223250023808</v>
+        <v>0.40414911088375</v>
       </c>
       <c r="Z78" t="n">
-        <v>-33.60324021463077</v>
+        <v>-33.80566916903211</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -14845,7 +14837,7 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>sem sinal (-4.1% do topo; Em Alta)</t>
+          <t>sem sinal (-4.4% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -14885,7 +14877,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -14914,42 +14906,38 @@
         <v>9.51</v>
       </c>
       <c r="T79" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+        <v>3.490000009536743</v>
+      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="W79" t="n">
-        <v>3.519999980926514</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="X79" t="n">
-        <v>-0.5681812794001595</v>
+        <v>-1.966290291233652</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.2131007047928472</v>
+        <v>0.2271925300616161</v>
       </c>
       <c r="Z79" t="n">
-        <v>-44.44444612640967</v>
+        <v>-44.60317612895736</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
       </c>
       <c r="AB79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="b">
         <v>0</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-2.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -15033,10 +15021,10 @@
         <v>-0.3150610655036079</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.4969509973032725</v>
+        <v>0.5140296514521071</v>
       </c>
       <c r="Z80" t="n">
-        <v>-33.6461812584439</v>
+        <v>-33.64618673068459</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -15131,7 +15119,7 @@
         <v>-6.696432800393303</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.3170723846765357</v>
+        <v>0.335723697898606</v>
       </c>
       <c r="Z81" t="n">
         <v>-45.32374311618977</v>
@@ -15185,7 +15173,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -15210,42 +15198,38 @@
         <v>0.15</v>
       </c>
       <c r="T82" t="n">
-        <v>21.97999954223633</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+        <v>21.95000076293945</v>
+      </c>
+      <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="W82" t="n">
-        <v>21.85000038146973</v>
+        <v>22</v>
       </c>
       <c r="X82" t="n">
-        <v>0.5949618237849119</v>
+        <v>-0.2272692593661252</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.6133080422800434</v>
+        <v>0.6160498202066319</v>
       </c>
       <c r="Z82" t="n">
-        <v>-14.24112266112576</v>
+        <v>-14.35816823381073</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
       </c>
       <c r="AB82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="b">
         <v>0</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -15308,25 +15292,25 @@
         <v>1.43</v>
       </c>
       <c r="T83" t="n">
-        <v>19.57999992370605</v>
+        <v>19.55999946594238</v>
       </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="W83" t="n">
         <v>22.04433250427246</v>
       </c>
       <c r="X83" t="n">
-        <v>-11.17898480295917</v>
+        <v>-11.26971314667198</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.357206353652937</v>
+        <v>1.38670932442204</v>
       </c>
       <c r="Z83" t="n">
-        <v>-11.57304503564538</v>
+        <v>-11.66337085713802</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -15339,7 +15323,7 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>sem sinal (-11.2% do topo; Lateral)</t>
+          <t>sem sinal (-11.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15363,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -15410,24 +15394,20 @@
       <c r="T84" t="n">
         <v>0.1700000017881393</v>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="W84" t="n">
-        <v>0.1599999964237213</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="X84" t="n">
-        <v>6.250003492459744</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.5297703105138586</v>
+        <v>0.5936072597001384</v>
       </c>
       <c r="Z84" t="n">
         <v>-99.12280697033108</v>
@@ -15436,14 +15416,14 @@
         <v>0</v>
       </c>
       <c r="AB84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="b">
         <v>0</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15505,7 @@
         <v>-1.338827125954645</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.536984982263352</v>
+        <v>0.548082198440202</v>
       </c>
       <c r="Z85" t="n">
         <v>-32.8754144263225</v>
@@ -15579,7 +15559,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -15604,13 +15584,9 @@
         <v>0.33</v>
       </c>
       <c r="T86" t="n">
-        <v>57.43000030517578</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+        <v>57.40000152587891</v>
+      </c>
+      <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr">
         <is>
           <t>Em Alta</t>
@@ -15620,26 +15596,26 @@
         <v>57.95000076293945</v>
       </c>
       <c r="X86" t="n">
-        <v>-0.8973260585291021</v>
+        <v>-0.9490927175488273</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.3695598150896612</v>
+        <v>0.3836662836524219</v>
       </c>
       <c r="Z86" t="n">
-        <v>-12.32061022110568</v>
+        <v>-12.36640988415434</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
       </c>
       <c r="AB86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="b">
         <v>0</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-0.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15684,7 @@
         <v>0.82</v>
       </c>
       <c r="T87" t="n">
-        <v>26.13999938964844</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -15724,13 +15700,13 @@
         <v>25.6299991607666</v>
       </c>
       <c r="X87" t="n">
-        <v>1.98985659610369</v>
+        <v>2.028874267618663</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.7259694265476809</v>
+        <v>0.7587732756253937</v>
       </c>
       <c r="Z87" t="n">
-        <v>-0.6461424543698913</v>
+        <v>-0.6081332218163871</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -15806,7 +15782,7 @@
         <v>-3.99</v>
       </c>
       <c r="T88" t="n">
-        <v>11.71000003814697</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr">
@@ -15818,13 +15794,13 @@
         <v>11.90999984741211</v>
       </c>
       <c r="X88" t="n">
-        <v>-1.679259545150991</v>
+        <v>-1.511337594306461</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.5769596860402114</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="Z88" t="n">
-        <v>-72.55039831216187</v>
+        <v>-72.50351714910308</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -15837,7 +15813,7 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>sem sinal (-1.7% do topo; Lateral)</t>
+          <t>sem sinal (-1.5% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15882,7 @@
         <v>0.46</v>
       </c>
       <c r="T89" t="n">
-        <v>20.02000045776367</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
@@ -15918,13 +15894,13 @@
         <v>21.29999923706055</v>
       </c>
       <c r="X89" t="n">
-        <v>-6.009384155609565</v>
+        <v>-6.197181887816738</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.6823740552728168</v>
+        <v>0.7087675151124646</v>
       </c>
       <c r="Z89" t="n">
-        <v>-24.17753906396563</v>
+        <v>-24.32903595635464</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -15937,7 +15913,7 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>sem sinal (-6.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -16006,7 +15982,7 @@
         <v>0.09</v>
       </c>
       <c r="T90" t="n">
-        <v>35.68999862670898</v>
+        <v>35.70000076293945</v>
       </c>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
@@ -16018,13 +15994,13 @@
         <v>36.13000106811523</v>
       </c>
       <c r="X90" t="n">
-        <v>-1.217831243837275</v>
+        <v>-1.190147501975181</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.2634790680518159</v>
+        <v>0.2800924597314911</v>
       </c>
       <c r="Z90" t="n">
-        <v>-2.566209156418731</v>
+        <v>-2.538903297999917</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -16106,7 +16082,7 @@
         <v>0.46</v>
       </c>
       <c r="T91" t="n">
-        <v>12.39999961853027</v>
+        <v>12.38000011444092</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -16122,13 +16098,13 @@
         <v>11.93000030517578</v>
       </c>
       <c r="X91" t="n">
-        <v>3.939642089955231</v>
+        <v>3.772001657618618</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.7999183916885073</v>
+        <v>0.7337404146549276</v>
       </c>
       <c r="Z91" t="n">
-        <v>-23.9043386413588</v>
+        <v>-24.02707053953161</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -16217,13 +16193,13 @@
         </is>
       </c>
       <c r="W92" t="n">
-        <v>66.26999664306641</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="X92" t="n">
-        <v>-3.244294560726102</v>
+        <v>-2.995455027603755</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.4610543545747023</v>
+        <v>0.4812084944902576</v>
       </c>
       <c r="Z92" t="n">
         <v>-5.455613336613685</v>
@@ -16239,7 +16215,7 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>sem sinal (-3.2% do topo; Em Alta)</t>
+          <t>sem sinal (-3.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -16306,7 +16282,7 @@
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="n">
-        <v>13.4399995803833</v>
+        <v>13.43000030517578</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -16322,13 +16298,13 @@
         <v>13.96000003814697</v>
       </c>
       <c r="X93" t="n">
-        <v>-3.724931635692863</v>
+        <v>-3.796559681396272</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.5586073029051598</v>
+        <v>0.6038505859337614</v>
       </c>
       <c r="Z93" t="n">
-        <v>-31.00616069706349</v>
+        <v>-31.05749167982783</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -16410,7 +16386,7 @@
         <v>-8.1</v>
       </c>
       <c r="T94" t="n">
-        <v>7.559999942779541</v>
+        <v>7.539999961853027</v>
       </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
@@ -16422,13 +16398,13 @@
         <v>8.060000419616699</v>
       </c>
       <c r="X94" t="n">
-        <v>-6.20347953853998</v>
+        <v>-6.4516182467941</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.6309269162210339</v>
+        <v>0.6459616681591288</v>
       </c>
       <c r="Z94" t="n">
-        <v>-48.25211410587148</v>
+        <v>-48.38901314538251</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -16441,7 +16417,7 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>sem sinal (-6.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -16508,7 +16484,7 @@
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="n">
-        <v>20.28000068664551</v>
+        <v>20.31999969482422</v>
       </c>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
@@ -16517,16 +16493,16 @@
         </is>
       </c>
       <c r="W95" t="n">
-        <v>21.07999992370605</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="X95" t="n">
-        <v>-3.795062808140182</v>
+        <v>-4.015117517271771</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.2619840213049268</v>
+        <v>0.2637961394066248</v>
       </c>
       <c r="Z95" t="n">
-        <v>-19.27891350751459</v>
+        <v>-19.11970427233278</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -16539,7 +16515,7 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>sem sinal (-3.8% do topo; Lateral)</t>
+          <t>sem sinal (-4.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16584,7 @@
         <v>0.48</v>
       </c>
       <c r="T96" t="n">
-        <v>39.09000015258789</v>
+        <v>39.04999923706055</v>
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
@@ -16620,13 +16596,13 @@
         <v>40.54000091552734</v>
       </c>
       <c r="X96" t="n">
-        <v>-3.576716157359738</v>
+        <v>-3.675386395702096</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.6661626914849412</v>
+        <v>0.6988575455886098</v>
       </c>
       <c r="Z96" t="n">
-        <v>-25.80797907587882</v>
+        <v>-25.88389999555658</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -16639,7 +16615,7 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -16723,7 +16699,7 @@
         <v>-5.954824818640314</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.9030973902304007</v>
+        <v>0.9362817222084994</v>
       </c>
       <c r="Z97" t="n">
         <v>-56.50522279345071</v>
@@ -16821,7 +16797,7 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.4775896989222487</v>
+        <v>0.4959029191028416</v>
       </c>
       <c r="Z98" t="n">
         <v>-29.58904476455676</v>
@@ -16877,7 +16853,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -16906,38 +16882,42 @@
         <v>0.09</v>
       </c>
       <c r="T99" t="n">
-        <v>8.680000305175781</v>
-      </c>
-      <c r="U99" t="inlineStr"/>
+        <v>8.670000076293945</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="V99" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="W99" t="n">
-        <v>8.710000038146973</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="X99" t="n">
-        <v>-0.3444286204340119</v>
+        <v>0.1154760861205473</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.4204158502482546</v>
+        <v>0.4408162954608456</v>
       </c>
       <c r="Z99" t="n">
-        <v>-18.24971257466952</v>
+        <v>-18.34389708580619</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
       </c>
       <c r="AB99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC99" t="b">
         <v>0</v>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>sem sinal (-0.3% do topo; Em Baixa)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -17021,7 +17001,7 @@
         <v>-4.142014797751925</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.8742141824747063</v>
+        <v>0.8974898570184661</v>
       </c>
       <c r="Z100" t="n">
         <v>-42.26183979448152</v>
@@ -17104,7 +17084,7 @@
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="n">
-        <v>30.1299991607666</v>
+        <v>30.09000015258789</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
@@ -17113,16 +17093,16 @@
         </is>
       </c>
       <c r="W101" t="n">
-        <v>32.43999862670898</v>
+        <v>32.27000045776367</v>
       </c>
       <c r="X101" t="n">
-        <v>-7.12083712617817</v>
+        <v>-6.755501314693369</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.3102502974133269</v>
+        <v>0.3148063792073904</v>
       </c>
       <c r="Z101" t="n">
-        <v>-22.38033148894612</v>
+        <v>-22.48337529386082</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -17135,7 +17115,7 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17204,7 +17184,7 @@
         <v>14.06</v>
       </c>
       <c r="T102" t="n">
-        <v>3.519999980926514</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
@@ -17216,13 +17196,13 @@
         <v>3.990000009536743</v>
       </c>
       <c r="X102" t="n">
-        <v>-11.77944931044746</v>
+        <v>-12.03007563724834</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.6014511398137189</v>
+        <v>0.5983060735912447</v>
       </c>
       <c r="Z102" t="n">
-        <v>-26.66666997803569</v>
+        <v>-26.87500310440846</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -17235,7 +17215,7 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>sem sinal (-11.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17282,7 @@
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="n">
-        <v>5.110000133514404</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
@@ -17314,13 +17294,13 @@
         <v>5.159999847412109</v>
       </c>
       <c r="X103" t="n">
-        <v>-0.9689867320980872</v>
+        <v>-1.162789623135996</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.6308751791821315</v>
+        <v>0.6457865161456435</v>
       </c>
       <c r="Z103" t="n">
-        <v>-55.35071957973965</v>
+        <v>-55.43809785996384</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -17333,7 +17313,7 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>sem sinal (-1.0% do topo; Em Alta)</t>
+          <t>sem sinal (-1.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17380,7 @@
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="n">
-        <v>50.36999893188477</v>
+        <v>50.38999938964844</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -17416,13 +17396,13 @@
         <v>51.63999938964844</v>
       </c>
       <c r="X104" t="n">
-        <v>-2.459334765248378</v>
+        <v>-2.420604211414012</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.4336958976780824</v>
+        <v>0.4767958077733461</v>
       </c>
       <c r="Z104" t="n">
-        <v>-14.98734357487803</v>
+        <v>-14.95358752801952</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -17502,7 +17482,7 @@
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="n">
-        <v>4.769999980926514</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
@@ -17514,13 +17494,13 @@
         <v>5.389999866485596</v>
       </c>
       <c r="X105" t="n">
-        <v>-11.50278109307888</v>
+        <v>-11.68830525434751</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.1821180384252146</v>
+        <v>0.185252014916396</v>
       </c>
       <c r="Z105" t="n">
-        <v>-34.70084124298338</v>
+        <v>-34.83773336015471</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -17533,7 +17513,7 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>sem sinal (-11.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-11.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17654,7 @@
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="n">
-        <v>11.63000011444092</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
@@ -17686,13 +17666,13 @@
         <v>15.56999969482422</v>
       </c>
       <c r="X107" t="n">
-        <v>-25.30507166093932</v>
+        <v>-25.43352675506703</v>
       </c>
       <c r="Y107" t="n">
-        <v>0.6914205453684131</v>
+        <v>0.6764284153238488</v>
       </c>
       <c r="Z107" t="n">
-        <v>-35.0279309369291</v>
+        <v>-35.13966534022465</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -17705,7 +17685,7 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>sem sinal (-25.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-25.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17752,7 @@
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="n">
-        <v>18.64999961853027</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
@@ -17784,13 +17764,13 @@
         <v>19.6299991607666</v>
       </c>
       <c r="X108" t="n">
-        <v>-4.99235651621931</v>
+        <v>-5.094243722631663</v>
       </c>
       <c r="Y108" t="n">
-        <v>0.3641865240179392</v>
+        <v>0.4125961905801452</v>
       </c>
       <c r="Z108" t="n">
-        <v>-18.02197969876803</v>
+        <v>-18.10989379882812</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -17803,7 +17783,7 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>sem sinal (-5.0% do topo; Em Alta)</t>
+          <t>sem sinal (-5.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17867,7 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0.5595122785026494</v>
+        <v>0.5429592644129765</v>
       </c>
       <c r="Z109" t="n">
         <v>-18.23444274764853</v>
@@ -17970,7 +17950,7 @@
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="n">
-        <v>19.20999908447266</v>
+        <v>19.19000053405762</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -17986,13 +17966,13 @@
         <v>18.85000038146973</v>
       </c>
       <c r="X110" t="n">
-        <v>1.909807404337371</v>
+        <v>1.803714300834303</v>
       </c>
       <c r="Y110" t="n">
-        <v>0.6008179959100205</v>
+        <v>0.6383000794129207</v>
       </c>
       <c r="Z110" t="n">
-        <v>-29.18540556240793</v>
+        <v>-29.25912702542067</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -18163,7 +18143,7 @@
         <v>-3.17072875722394</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.189774037418629</v>
+        <v>1.209892109550882</v>
       </c>
       <c r="Z112" t="n">
         <v>-50.56039650525263</v>
@@ -18248,7 +18228,7 @@
         <v>1.18</v>
       </c>
       <c r="T113" t="n">
-        <v>57.95999908447266</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
@@ -18257,16 +18237,16 @@
         </is>
       </c>
       <c r="W113" t="n">
-        <v>60.54000091552734</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="X113" t="n">
-        <v>-4.261648153350073</v>
+        <v>-4.765813942320774</v>
       </c>
       <c r="Y113" t="n">
-        <v>0.8881550100421148</v>
+        <v>0.9417554981502457</v>
       </c>
       <c r="Z113" t="n">
-        <v>-20.58098599831585</v>
+        <v>-20.59468608200082</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -18279,7 +18259,7 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>sem sinal (-4.3% do topo; Em Alta)</t>
+          <t>sem sinal (-4.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18326,7 @@
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="n">
-        <v>4.730000019073486</v>
+        <v>4.710000038146973</v>
       </c>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
@@ -18358,13 +18338,13 @@
         <v>5.710000038146973</v>
       </c>
       <c r="X114" t="n">
-        <v>-17.1628723734916</v>
+        <v>-17.51313473413781</v>
       </c>
       <c r="Y114" t="n">
-        <v>0.916517213502709</v>
+        <v>0.9347077274389188</v>
       </c>
       <c r="Z114" t="n">
-        <v>-58.2155464082198</v>
+        <v>-58.39222468971885</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -18377,7 +18357,7 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>sem sinal (-17.2% do topo; Lateral)</t>
+          <t>sem sinal (-17.5% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -18459,7 +18439,7 @@
         <v>-5.209112060703136</v>
       </c>
       <c r="Y115" t="n">
-        <v>0.2997812330926113</v>
+        <v>0.3286243145126191</v>
       </c>
       <c r="Z115" t="n">
         <v>-46.50907768076634</v>
@@ -18559,7 +18539,7 @@
         <v>-4.469269576030488</v>
       </c>
       <c r="Y116" t="n">
-        <v>0.2090539930816664</v>
+        <v>0.2184075107043249</v>
       </c>
       <c r="Z116" t="n">
         <v>-61.13636361173362</v>
@@ -18642,7 +18622,7 @@
         <v>-0</v>
       </c>
       <c r="T117" t="n">
-        <v>5.960000038146973</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
@@ -18651,16 +18631,16 @@
         </is>
       </c>
       <c r="W117" t="n">
-        <v>6.940000057220459</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="X117" t="n">
-        <v>-14.12103762238276</v>
+        <v>-13.17716113354037</v>
       </c>
       <c r="Y117" t="n">
-        <v>0.3873111827167007</v>
+        <v>0.4017064228792032</v>
       </c>
       <c r="Z117" t="n">
-        <v>-56.74891035094453</v>
+        <v>-56.96661869920067</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -18673,7 +18653,7 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>sem sinal (-14.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -18742,7 +18722,7 @@
         <v>16.93</v>
       </c>
       <c r="T118" t="n">
-        <v>18.20999908447266</v>
+        <v>18.18000030517578</v>
       </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
@@ -18751,16 +18731,16 @@
         </is>
       </c>
       <c r="W118" t="n">
-        <v>18.23999977111816</v>
+        <v>18.25</v>
       </c>
       <c r="X118" t="n">
-        <v>-0.164477450778322</v>
+        <v>-0.3835599716395577</v>
       </c>
       <c r="Y118" t="n">
-        <v>0.4175377146895259</v>
+        <v>0.4117271862322164</v>
       </c>
       <c r="Z118" t="n">
-        <v>-14.30588666130514</v>
+        <v>-14.44705738740809</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -18773,7 +18753,7 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Em Alta)</t>
+          <t>sem sinal (-0.4% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -18851,13 +18831,13 @@
         </is>
       </c>
       <c r="W119" t="n">
-        <v>14.27999973297119</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="X119" t="n">
-        <v>-1.120447131680857</v>
+        <v>-2.21606443298612</v>
       </c>
       <c r="Y119" t="n">
-        <v>0.8497446772092315</v>
+        <v>0.892759085631061</v>
       </c>
       <c r="Z119" t="n">
         <v>-18.51651739090506</v>
@@ -18873,7 +18853,7 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18937,7 @@
         <v>-3.472227051302046</v>
       </c>
       <c r="Y120" t="n">
-        <v>0.2032029292637607</v>
+        <v>0.2090862327485252</v>
       </c>
       <c r="Z120" t="n">
         <v>-50.17921130107499</v>
@@ -19042,7 +19022,7 @@
         <v>1350.91</v>
       </c>
       <c r="T121" t="n">
-        <v>18.73999977111816</v>
+        <v>18.75</v>
       </c>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
@@ -19054,13 +19034,13 @@
         <v>23.09000015258789</v>
       </c>
       <c r="X121" t="n">
-        <v>-18.83932591045127</v>
+        <v>-18.79601612779318</v>
       </c>
       <c r="Y121" t="n">
-        <v>2.635898197930457</v>
+        <v>2.586608130188648</v>
       </c>
       <c r="Z121" t="n">
-        <v>-33.89685019308995</v>
+        <v>-33.86157555936781</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -19140,7 +19120,7 @@
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="n">
-        <v>39.09999847412109</v>
+        <v>39.04000091552734</v>
       </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
@@ -19152,13 +19132,13 @@
         <v>40.95000076293945</v>
       </c>
       <c r="X122" t="n">
-        <v>-4.517710022835086</v>
+        <v>-4.664224204705503</v>
       </c>
       <c r="Y122" t="n">
-        <v>0.4197047989142804</v>
+        <v>0.4313509873370244</v>
       </c>
       <c r="Z122" t="n">
-        <v>-15.58722208176069</v>
+        <v>-15.71675049063167</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -19171,7 +19151,7 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>sem sinal (-4.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19237,7 @@
         <v>-3.832749110873113</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.436003939822815</v>
+        <v>1.49917183676178</v>
       </c>
       <c r="Z123" t="n">
         <v>-39.99999896339747</v>
@@ -19340,7 +19320,7 @@
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="n">
-        <v>15.77999973297119</v>
+        <v>15.77000045776367</v>
       </c>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
@@ -19352,13 +19332,13 @@
         <v>16.19000053405762</v>
       </c>
       <c r="X124" t="n">
-        <v>-2.532432288831243</v>
+        <v>-2.594194332547572</v>
       </c>
       <c r="Y124" t="n">
-        <v>0.4751457502301319</v>
+        <v>0.4805231514373677</v>
       </c>
       <c r="Z124" t="n">
-        <v>-7.231043382481483</v>
+        <v>-7.289828068389603</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -19371,7 +19351,7 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>sem sinal (-2.5% do topo; Lateral)</t>
+          <t>sem sinal (-2.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -19514,7 +19494,7 @@
         <v>4.36</v>
       </c>
       <c r="T126" t="n">
-        <v>18.92000007629395</v>
+        <v>18.93000030517578</v>
       </c>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
@@ -19526,13 +19506,13 @@
         <v>21</v>
       </c>
       <c r="X126" t="n">
-        <v>-9.904761541457408</v>
+        <v>-9.857141403924851</v>
       </c>
       <c r="Y126" t="n">
-        <v>0.8583242794145842</v>
+        <v>0.8696904651435505</v>
       </c>
       <c r="Z126" t="n">
-        <v>-14.56313829774738</v>
+        <v>-14.51798036072185</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -19610,7 +19590,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="n">
-        <v>0.300000011920929</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
@@ -19619,16 +19599,16 @@
         </is>
       </c>
       <c r="W127" t="n">
-        <v>0.3300000131130219</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="X127" t="n">
-        <v>-9.090909090909093</v>
+        <v>-6.451616314521791</v>
       </c>
       <c r="Y127" t="n">
-        <v>3.074487776855812</v>
+        <v>3.276870493148599</v>
       </c>
       <c r="Z127" t="n">
-        <v>-79.16666666666666</v>
+        <v>-79.86111249084821</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -19641,7 +19621,7 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>sem sinal (-9.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -19710,25 +19690,25 @@
         <v>35.16</v>
       </c>
       <c r="T128" t="n">
-        <v>5.150000095367432</v>
+        <v>5.130000114440918</v>
       </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="W128" t="n">
         <v>5.190000057220459</v>
       </c>
       <c r="X128" t="n">
-        <v>-0.770712165934917</v>
+        <v>-1.156068248902375</v>
       </c>
       <c r="Y128" t="n">
-        <v>0.3171425057059684</v>
+        <v>0.3287736144888957</v>
       </c>
       <c r="Z128" t="n">
-        <v>-17.20256802116788</v>
+        <v>-17.52411113372638</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -19741,7 +19721,7 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-1.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -19810,7 +19790,7 @@
         <v>3.04</v>
       </c>
       <c r="T129" t="n">
-        <v>71</v>
+        <v>71.05999755859375</v>
       </c>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
@@ -19822,13 +19802,13 @@
         <v>75.94000244140625</v>
       </c>
       <c r="X129" t="n">
-        <v>-6.505138639174857</v>
+        <v>-6.426132112094429</v>
       </c>
       <c r="Y129" t="n">
-        <v>0.5364528354128091</v>
+        <v>0.5396175443663827</v>
       </c>
       <c r="Z129" t="n">
-        <v>-16.37220409429788</v>
+        <v>-16.30153559310185</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -19841,7 +19821,7 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>sem sinal (-6.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -19910,7 +19890,7 @@
         <v>-2.22</v>
       </c>
       <c r="T130" t="n">
-        <v>11.21000003814697</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
@@ -19919,16 +19899,16 @@
         </is>
       </c>
       <c r="W130" t="n">
-        <v>12.31999969482422</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="X130" t="n">
-        <v>-9.009737696207655</v>
+        <v>-8.854590702132814</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.148069181397499</v>
+        <v>1.127904009056012</v>
       </c>
       <c r="Z130" t="n">
-        <v>-23.53342322765546</v>
+        <v>-23.46520884166691</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -19941,7 +19921,7 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>sem sinal (-9.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-8.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -20010,7 +19990,7 @@
         <v>118.1</v>
       </c>
       <c r="T131" t="n">
-        <v>11.07999992370605</v>
+        <v>11.09000015258789</v>
       </c>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
@@ -20022,13 +20002,13 @@
         <v>11.10999965667725</v>
       </c>
       <c r="X131" t="n">
-        <v>-0.270024607544983</v>
+        <v>-0.1800135437208139</v>
       </c>
       <c r="Y131" t="n">
-        <v>0.7645580120277782</v>
+        <v>0.7389986487966986</v>
       </c>
       <c r="Z131" t="n">
-        <v>-0.3597118908694741</v>
+        <v>-0.2697817741001085</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -20041,7 +20021,7 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>sem sinal (-0.3% do topo; Em Alta)</t>
+          <t>sem sinal (-0.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -20110,7 +20090,7 @@
         <v>-0</v>
       </c>
       <c r="T132" t="n">
-        <v>2.460000038146973</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
@@ -20122,13 +20102,13 @@
         <v>2.539999961853027</v>
       </c>
       <c r="X132" t="n">
-        <v>-3.149603342816265</v>
+        <v>-3.543303760668293</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.964350245470331</v>
+        <v>1.846796851798884</v>
       </c>
       <c r="Z132" t="n">
-        <v>-81.64179023747772</v>
+        <v>-81.71641703410411</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -20141,7 +20121,7 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Lateral)</t>
+          <t>sem sinal (-3.5% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20161,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -20210,38 +20190,42 @@
         <v>1.12</v>
       </c>
       <c r="T133" t="n">
-        <v>26.96999931335449</v>
-      </c>
-      <c r="U133" t="inlineStr"/>
+        <v>26.89999961853027</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="W133" t="n">
         <v>27.17000007629395</v>
       </c>
       <c r="X133" t="n">
-        <v>-0.7361088052184273</v>
+        <v>-0.993744781028727</v>
       </c>
       <c r="Y133" t="n">
-        <v>0.3313724208412916</v>
+        <v>0.3413389864660427</v>
       </c>
       <c r="Z133" t="n">
-        <v>-4.089621235979513</v>
+        <v>-4.338553286957813</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
       </c>
       <c r="AB133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC133" t="b">
         <v>0</v>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>sem sinal (-0.7% do topo; Em Baixa)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -20308,7 +20292,7 @@
       </c>
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="n">
-        <v>0.6299999952316284</v>
+        <v>0.6399999856948853</v>
       </c>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
@@ -20320,13 +20304,13 @@
         <v>0.9599999785423279</v>
       </c>
       <c r="X134" t="n">
-        <v>-34.3749990298723</v>
+        <v>-33.33333333333334</v>
       </c>
       <c r="Y134" t="n">
-        <v>0.7766264579593294</v>
+        <v>0.7783254197933961</v>
       </c>
       <c r="Z134" t="n">
-        <v>-89.13793147389867</v>
+        <v>-88.81118865087507</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -20339,7 +20323,7 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>sem sinal (-34.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-33.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>

--- a/reports/screener_2026-08-04.xlsx
+++ b/reports/screener_2026-08-04.xlsx
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW5" t="n">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="AX7" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.41281066323299</v>
       </c>
       <c r="AY7" t="n">
         <v>-39.50409545018086</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="AX10" t="n">
-        <v>-16.54525760371704</v>
+        <v>-14.90715866883865</v>
       </c>
       <c r="AY10" t="n">
         <v>-54.13720844041888</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -2773,7 +2773,7 @@
         <v>-3.612203515041446</v>
       </c>
       <c r="AY13" t="n">
-        <v>-22.7763666994001</v>
+        <v>-22.77636138240788</v>
       </c>
       <c r="AZ13" t="b">
         <v>1</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.30768966674805</v>
+        <v>-12.4901748318072</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="AW16" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="AX16" t="n">
-        <v>-1.277582454837922</v>
+        <v>-2.118835116863982</v>
       </c>
       <c r="AY16" t="n">
         <v>-13.54395936495905</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-2.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.129361865388501</v>
+        <v>-1.814843745989081</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="AW25" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="AX25" t="n">
-        <v>-3.49544105988292</v>
+        <v>-3.053439393562163</v>
       </c>
       <c r="AY25" t="n">
         <v>-39.52381043207078</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY27" t="n">
-        <v>-39.5192605242667</v>
+        <v>-39.51925229062647</v>
       </c>
       <c r="AZ27" t="b">
         <v>1</v>
@@ -6557,7 +6557,7 @@
       <c r="AU35" t="inlineStr"/>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW35" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
         <v>-3.347322770539629</v>
       </c>
       <c r="AY36" t="n">
-        <v>-12.30894652743484</v>
+        <v>-12.30895602838301</v>
       </c>
       <c r="AZ36" t="b">
         <v>1</v>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="AX38" t="n">
-        <v>-2.285715311515235</v>
+        <v>-2.252858377438904</v>
       </c>
       <c r="AY38" t="n">
         <v>-17.59775069846685</v>
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-1.98511558212644</v>
       </c>
       <c r="AY39" t="n">
         <v>-47.92224740248528</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="AW41" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="AX41" t="n">
-        <v>-3.418800283779255</v>
+        <v>-3.004289078750577</v>
       </c>
       <c r="AY41" t="n">
         <v>-52.18694930098489</v>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
         <v>-3.855259824575719</v>
       </c>
       <c r="AY47" t="n">
-        <v>-14.20840116822351</v>
+        <v>-14.20839330687329</v>
       </c>
       <c r="AZ47" t="b">
         <v>1</v>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="AW49" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>-0.5291042223046771</v>
       </c>
       <c r="AY49" t="n">
         <v>-15.4147281673955</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="AX50" t="n">
-        <v>-14.84423417392992</v>
+        <v>-13.52358030617676</v>
       </c>
       <c r="AY50" t="n">
         <v>-34.85117715011583</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9321,14 +9321,14 @@
       <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="AX51" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-0.6925190193304398</v>
       </c>
       <c r="AY51" t="n">
         <v>-27.87197279000151</v>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY54" t="n">
-        <v>-23.4739172343906</v>
+        <v>-23.47392377028176</v>
       </c>
       <c r="AZ54" t="b">
         <v>1</v>
@@ -10846,7 +10846,7 @@
       <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW60" t="n">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="AW64" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="AX64" t="n">
-        <v>-3.506767262291599</v>
+        <v>-3.465848880756128</v>
       </c>
       <c r="AY64" t="n">
-        <v>-13.58725425550743</v>
+        <v>-13.55060269313266</v>
       </c>
       <c r="AZ64" t="b">
         <v>1</v>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="AW66" t="n">
-        <v>76.08999633789062</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="AX66" t="n">
-        <v>0.2891329100952689</v>
+        <v>0.03932718901014098</v>
       </c>
       <c r="AY66" t="n">
         <v>-16.71033041805866</v>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW5" t="n">
@@ -13356,10 +13356,10 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="AX7" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.41281066323299</v>
       </c>
       <c r="AY7" t="n">
         <v>-39.50409545018086</v>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="AX10" t="n">
-        <v>-16.54525760371704</v>
+        <v>-14.90715866883865</v>
       </c>
       <c r="AY10" t="n">
         <v>-54.13720844041888</v>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14394,7 +14394,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -14404,7 +14404,7 @@
         <v>-3.612203515041446</v>
       </c>
       <c r="AY13" t="n">
-        <v>-22.7763666994001</v>
+        <v>-22.77636138240788</v>
       </c>
       <c r="AZ13" t="b">
         <v>1</v>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -14575,10 +14575,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.30768966674805</v>
+        <v>-12.4901748318072</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="AW16" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="AX16" t="n">
-        <v>-1.277582454837922</v>
+        <v>-2.118835116863982</v>
       </c>
       <c r="AY16" t="n">
         <v>-13.54395936495905</v>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-2.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -15967,10 +15967,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.129361865388501</v>
+        <v>-1.814843745989081</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="AW26" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="AX26" t="n">
-        <v>-3.49544105988292</v>
+        <v>-3.053439393562163</v>
       </c>
       <c r="AY26" t="n">
         <v>-39.52381043207078</v>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17021,7 +17021,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY28" t="n">
-        <v>-39.5192605242667</v>
+        <v>-39.51925229062647</v>
       </c>
       <c r="AZ28" t="b">
         <v>1</v>
@@ -18355,7 +18355,7 @@
       <c r="AU36" t="inlineStr"/>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW36" t="n">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
         <v>-3.347322770539629</v>
       </c>
       <c r="AY37" t="n">
-        <v>-12.30894652743484</v>
+        <v>-12.30895602838301</v>
       </c>
       <c r="AZ37" t="b">
         <v>1</v>
@@ -18874,10 +18874,10 @@
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="AX39" t="n">
-        <v>-2.285715311515235</v>
+        <v>-2.252858377438904</v>
       </c>
       <c r="AY39" t="n">
         <v>-17.59775069846685</v>
@@ -19047,10 +19047,10 @@
         </is>
       </c>
       <c r="AW40" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="AX40" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-1.98511558212644</v>
       </c>
       <c r="AY40" t="n">
         <v>-47.92224740248528</v>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -19401,10 +19401,10 @@
         </is>
       </c>
       <c r="AW42" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="AX42" t="n">
-        <v>-3.418800283779255</v>
+        <v>-3.004289078750577</v>
       </c>
       <c r="AY42" t="n">
         <v>-52.18694930098489</v>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -20437,7 +20437,7 @@
         <v>-3.855259824575719</v>
       </c>
       <c r="AY48" t="n">
-        <v>-14.20840116822351</v>
+        <v>-14.20839330687329</v>
       </c>
       <c r="AZ48" t="b">
         <v>1</v>
@@ -20773,10 +20773,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>-0.5291042223046771</v>
       </c>
       <c r="AY50" t="n">
         <v>-15.4147281673955</v>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -20950,10 +20950,10 @@
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="AX51" t="n">
-        <v>-14.84423417392992</v>
+        <v>-13.52358030617676</v>
       </c>
       <c r="AY51" t="n">
         <v>-34.85117715011583</v>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -21119,14 +21119,14 @@
       <c r="AU52" t="inlineStr"/>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW52" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="AX52" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-0.6925190193304398</v>
       </c>
       <c r="AY52" t="n">
         <v>-27.87197279000151</v>
@@ -21142,7 +21142,7 @@
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21660,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY55" t="n">
-        <v>-23.4739172343906</v>
+        <v>-23.47392377028176</v>
       </c>
       <c r="AZ55" t="b">
         <v>1</v>
@@ -22644,7 +22644,7 @@
       <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW61" t="n">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -23296,13 +23296,13 @@
         </is>
       </c>
       <c r="AW65" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="AX65" t="n">
-        <v>-3.506767262291599</v>
+        <v>-3.465848880756128</v>
       </c>
       <c r="AY65" t="n">
-        <v>-13.58725425550743</v>
+        <v>-13.55060269313266</v>
       </c>
       <c r="AZ65" t="b">
         <v>1</v>
@@ -23650,10 +23650,10 @@
         </is>
       </c>
       <c r="AW67" t="n">
-        <v>76.08999633789062</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="AX67" t="n">
-        <v>0.2891329100952689</v>
+        <v>0.03932718901014098</v>
       </c>
       <c r="AY67" t="n">
         <v>-16.71033041805866</v>
@@ -23988,7 +23988,7 @@
         <v>-1.302573977731003</v>
       </c>
       <c r="AY69" t="n">
-        <v>-15.92982162987447</v>
+        <v>-15.92983151621281</v>
       </c>
       <c r="AZ69" t="b">
         <v>0</v>
@@ -24249,7 +24249,7 @@
         <v>1</v>
       </c>
       <c r="V71" t="n">
-        <v>98226323456</v>
+        <v>98502926336</v>
       </c>
       <c r="W71" t="n">
         <v>11.13</v>
@@ -24328,10 +24328,10 @@
         </is>
       </c>
       <c r="AW71" t="n">
-        <v>30.3700008392334</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="AX71" t="n">
-        <v>-7.770828268476048</v>
+        <v>-7.679630560276429</v>
       </c>
       <c r="AY71" t="n">
         <v>-20.69199954808616</v>
@@ -24347,7 +24347,7 @@
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24495,10 +24495,10 @@
         </is>
       </c>
       <c r="AW72" t="n">
-        <v>4.070000171661377</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="AX72" t="n">
-        <v>-4.422605876297203</v>
+        <v>-2.506263268008835</v>
       </c>
       <c r="AY72" t="n">
         <v>-19.0219927402037</v>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>sem sinal (-4.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24656,10 +24656,10 @@
         </is>
       </c>
       <c r="AW73" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="AX73" t="n">
-        <v>-1.316411286410224</v>
+        <v>-1.686185498450943</v>
       </c>
       <c r="AY73" t="n">
         <v>-23.79046311986899</v>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-1.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -25155,7 +25155,7 @@
       <c r="AU76" t="inlineStr"/>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW76" t="n">
@@ -25178,7 +25178,7 @@
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>sem sinal (-5.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.3% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -25564,7 +25564,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -25671,21 +25671,17 @@
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr"/>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU79" t="inlineStr"/>
       <c r="AV79" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW79" t="n">
-        <v>3.519999980926514</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="AX79" t="n">
-        <v>0.2840906397000742</v>
+        <v>-0.8426958391001382</v>
       </c>
       <c r="AY79" t="n">
         <v>-43.96825611876666</v>
@@ -25694,14 +25690,14 @@
         <v>0</v>
       </c>
       <c r="BA79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="b">
         <v>0</v>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -26085,7 +26081,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -26186,21 +26182,17 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr"/>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU82" t="inlineStr"/>
       <c r="AV82" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW82" t="n">
-        <v>21.85000038146973</v>
+        <v>22</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.09153527420819874</v>
+        <v>-0.5909052762118283</v>
       </c>
       <c r="AY82" t="n">
         <v>-14.67030216407054</v>
@@ -26209,14 +26201,14 @@
         <v>0</v>
       </c>
       <c r="BA82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="b">
         <v>0</v>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26350,7 @@
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW83" t="n">
@@ -26381,7 +26373,7 @@
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>sem sinal (-10.4% do topo; Lateral)</t>
+          <t>sem sinal (-10.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -26686,10 +26678,10 @@
         </is>
       </c>
       <c r="AW85" t="n">
-        <v>0.1599999964237213</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>-5.882356034843117</v>
       </c>
       <c r="AY85" t="n">
         <v>-99.17440658744904</v>
@@ -26705,7 +26697,7 @@
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -27867,10 +27859,10 @@
         </is>
       </c>
       <c r="AW92" t="n">
-        <v>66.26999664306641</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="AX92" t="n">
-        <v>-3.561184420100938</v>
+        <v>-3.313159874831761</v>
       </c>
       <c r="AY92" t="n">
         <v>-5.76526078591314</v>
@@ -27886,7 +27878,7 @@
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Alta)</t>
+          <t>sem sinal (-3.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -28376,10 +28368,10 @@
         </is>
       </c>
       <c r="AW95" t="n">
-        <v>21.07999992370605</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="AX95" t="n">
-        <v>-3.889941640379546</v>
+        <v>-4.298534927409481</v>
       </c>
       <c r="AY95" t="n">
         <v>-19.35852192104358</v>
@@ -28395,7 +28387,7 @@
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>sem sinal (-3.9% do topo; Lateral)</t>
+          <t>sem sinal (-4.3% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -29030,10 +29022,10 @@
         </is>
       </c>
       <c r="AW99" t="n">
-        <v>8.710000038146973</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="AX99" t="n">
-        <v>-0.5740550001823053</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
         <v>-18.43808159694287</v>
@@ -29049,7 +29041,7 @@
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29372,10 +29364,10 @@
         </is>
       </c>
       <c r="AW101" t="n">
-        <v>32.43999862670898</v>
+        <v>32.27000045776367</v>
       </c>
       <c r="AX101" t="n">
-        <v>-7.12083712617817</v>
+        <v>-6.631550252991147</v>
       </c>
       <c r="AY101" t="n">
         <v>-22.38033148894612</v>
@@ -29391,7 +29383,7 @@
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -31296,10 +31288,10 @@
         </is>
       </c>
       <c r="AW113" t="n">
-        <v>60.54000091552734</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="AX113" t="n">
-        <v>-3.452263166470892</v>
+        <v>-3.944121234780862</v>
       </c>
       <c r="AY113" t="n">
         <v>-19.90956690277227</v>
@@ -31315,7 +31307,7 @@
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Alta)</t>
+          <t>sem sinal (-3.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -31926,10 +31918,10 @@
         </is>
       </c>
       <c r="AW117" t="n">
-        <v>6.940000057220459</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="AX117" t="n">
-        <v>-15.99423810320502</v>
+        <v>-14.64128859693144</v>
       </c>
       <c r="AY117" t="n">
         <v>-57.6923074261264</v>
@@ -31945,7 +31937,7 @@
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>sem sinal (-16.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31977,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -32092,21 +32084,17 @@
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="inlineStr"/>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU118" t="inlineStr"/>
       <c r="AV118" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW118" t="n">
-        <v>18.23999977111816</v>
+        <v>18.25</v>
       </c>
       <c r="AX118" t="n">
-        <v>0.05482581692610733</v>
+        <v>0</v>
       </c>
       <c r="AY118" t="n">
         <v>-14.11764705882353</v>
@@ -32115,14 +32103,14 @@
         <v>0</v>
       </c>
       <c r="BA118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB118" t="b">
         <v>0</v>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -32276,10 +32264,10 @@
         </is>
       </c>
       <c r="AW119" t="n">
-        <v>14.27999973297119</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="AX119" t="n">
-        <v>-1.120447131680857</v>
+        <v>-2.21606443298612</v>
       </c>
       <c r="AY119" t="n">
         <v>-18.51651739090506</v>
@@ -32295,7 +32283,7 @@
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -33524,10 +33512,10 @@
         </is>
       </c>
       <c r="AW127" t="n">
-        <v>0.3300000131130219</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="AX127" t="n">
-        <v>-15.15151816185063</v>
+        <v>-9.677419664956521</v>
       </c>
       <c r="AY127" t="n">
         <v>-80.5555562454241</v>
@@ -33543,7 +33531,7 @@
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>sem sinal (-15.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-9.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -33689,7 +33677,7 @@
       <c r="AU128" t="inlineStr"/>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW128" t="n">
@@ -33712,7 +33700,7 @@
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Lateral)</t>
+          <t>sem sinal (-1.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -34017,10 +34005,10 @@
         </is>
       </c>
       <c r="AW130" t="n">
-        <v>12.31999969482422</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="AX130" t="n">
-        <v>-8.441558341027754</v>
+        <v>-8.367186446266416</v>
       </c>
       <c r="AY130" t="n">
         <v>-23.05593553629934</v>
@@ -34408,7 +34396,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -34443,7 +34431,7 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>51848818688</v>
+        <v>51957202944</v>
       </c>
       <c r="W133" t="n">
         <v>39.98</v>
@@ -34511,10 +34499,14 @@
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="inlineStr"/>
-      <c r="AU133" t="inlineStr"/>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW133" t="n">
@@ -34530,14 +34522,14 @@
         <v>0</v>
       </c>
       <c r="BA133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB133" t="b">
         <v>0</v>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>sem sinal (-0.0% do topo; Em Baixa)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -34677,7 +34669,7 @@
         <v>-35.41666472641126</v>
       </c>
       <c r="AY134" t="n">
-        <v>-89.31034509690564</v>
+        <v>-89.16083867989796</v>
       </c>
       <c r="AZ134" t="b">
         <v>0</v>

--- a/reports/screener_2026-08-04.xlsx
+++ b/reports/screener_2026-08-04.xlsx
@@ -5223,7 +5223,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY27" t="n">
-        <v>-39.51925229062647</v>
+        <v>-39.51924405698401</v>
       </c>
       <c r="AZ27" t="b">
         <v>1</v>
@@ -5694,7 +5694,7 @@
         <v>0.5876255599746028</v>
       </c>
       <c r="AY30" t="n">
-        <v>-20.18449126434217</v>
+        <v>-20.18448271439143</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -6732,7 +6732,7 @@
         <v>-3.347322770539629</v>
       </c>
       <c r="AY36" t="n">
-        <v>-12.30895602838301</v>
+        <v>-12.30894652743484</v>
       </c>
       <c r="AZ36" t="b">
         <v>1</v>
@@ -7082,7 +7082,7 @@
         <v>-2.252858377438904</v>
       </c>
       <c r="AY38" t="n">
-        <v>-17.59775069846685</v>
+        <v>-17.59775964860609</v>
       </c>
       <c r="AZ38" t="b">
         <v>1</v>
@@ -8639,7 +8639,7 @@
         <v>-3.855259824575719</v>
       </c>
       <c r="AY47" t="n">
-        <v>-14.20839330687329</v>
+        <v>-14.20840116822351</v>
       </c>
       <c r="AZ47" t="b">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>-0.9501178501326923</v>
       </c>
       <c r="AY58" t="n">
-        <v>-14.40870028403989</v>
+        <v>-14.40870883002358</v>
       </c>
       <c r="AZ58" t="b">
         <v>1</v>
@@ -10856,7 +10856,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY60" t="n">
-        <v>-50.51140229842947</v>
+        <v>-50.51140559404919</v>
       </c>
       <c r="AZ60" t="b">
         <v>1</v>
@@ -11033,7 +11033,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY61" t="n">
-        <v>-9.423147674714317</v>
+        <v>-9.423154175560278</v>
       </c>
       <c r="AZ61" t="b">
         <v>1</v>
@@ -17021,7 +17021,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY28" t="n">
-        <v>-39.51925229062647</v>
+        <v>-39.51924405698401</v>
       </c>
       <c r="AZ28" t="b">
         <v>1</v>
@@ -17492,7 +17492,7 @@
         <v>0.5876255599746028</v>
       </c>
       <c r="AY31" t="n">
-        <v>-20.18449126434217</v>
+        <v>-20.18448271439143</v>
       </c>
       <c r="AZ31" t="b">
         <v>1</v>
@@ -18530,7 +18530,7 @@
         <v>-3.347322770539629</v>
       </c>
       <c r="AY37" t="n">
-        <v>-12.30895602838301</v>
+        <v>-12.30894652743484</v>
       </c>
       <c r="AZ37" t="b">
         <v>1</v>
@@ -18880,7 +18880,7 @@
         <v>-2.252858377438904</v>
       </c>
       <c r="AY39" t="n">
-        <v>-17.59775069846685</v>
+        <v>-17.59775964860609</v>
       </c>
       <c r="AZ39" t="b">
         <v>1</v>
@@ -20437,7 +20437,7 @@
         <v>-3.855259824575719</v>
       </c>
       <c r="AY48" t="n">
-        <v>-14.20839330687329</v>
+        <v>-14.20840116822351</v>
       </c>
       <c r="AZ48" t="b">
         <v>1</v>
@@ -22304,7 +22304,7 @@
         <v>-0.9501178501326923</v>
       </c>
       <c r="AY59" t="n">
-        <v>-14.40870028403989</v>
+        <v>-14.40870883002358</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -22654,7 +22654,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY61" t="n">
-        <v>-50.51140229842947</v>
+        <v>-50.51140559404919</v>
       </c>
       <c r="AZ61" t="b">
         <v>1</v>
@@ -22831,7 +22831,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY62" t="n">
-        <v>-9.423147674714317</v>
+        <v>-9.423154175560278</v>
       </c>
       <c r="AZ62" t="b">
         <v>1</v>
@@ -23988,7 +23988,7 @@
         <v>-1.302573977731003</v>
       </c>
       <c r="AY69" t="n">
-        <v>-15.92983151621281</v>
+        <v>-15.92982162987447</v>
       </c>
       <c r="AZ69" t="b">
         <v>0</v>
@@ -27696,7 +27696,7 @@
         <v>4.274930948545386</v>
       </c>
       <c r="AY91" t="n">
-        <v>-23.6588689925551</v>
+        <v>-23.65887805399658</v>
       </c>
       <c r="AZ91" t="b">
         <v>0</v>
